--- a/research/traditional_assets/database/data/kenya/kenya_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_telecom_wireless.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1370509891548315</v>
+        <v>0.136671336187367</v>
       </c>
       <c r="C2">
-        <v>5681.94125444425</v>
+        <v>5648.552892613029</v>
       </c>
       <c r="D2">
-        <v>5455.74125444425</v>
+        <v>5478.534892613029</v>
       </c>
       <c r="E2">
-        <v>-345.9</v>
+        <v>-289.718</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>56.182</v>
       </c>
       <c r="G2">
         <v>226.2</v>
@@ -1457,28 +1457,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.8259546</v>
       </c>
       <c r="N2">
-        <v>572.2081632653062</v>
+        <v>569.3822086653062</v>
       </c>
       <c r="O2">
-        <v>171.6624489795919</v>
+        <v>170.8146625995919</v>
       </c>
       <c r="P2">
-        <v>400.5457142857143</v>
+        <v>398.5675460657143</v>
       </c>
       <c r="Q2">
-        <v>1003.745714285714</v>
+        <v>1001.767546065714</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1370509891548315</v>
+        <v>0.1376961981690576</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6407409627425109</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>202.4831408350673</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.136671336187367</v>
+        <v>0.1362916832199025</v>
       </c>
       <c r="C3">
-        <v>5648.552892613029</v>
+        <v>5615.355789736491</v>
       </c>
       <c r="D3">
-        <v>5478.534892613029</v>
+        <v>5501.519789736491</v>
       </c>
       <c r="E3">
-        <v>-289.718</v>
+        <v>-233.536</v>
       </c>
       <c r="F3">
-        <v>56.182</v>
+        <v>112.364</v>
       </c>
       <c r="G3">
         <v>226.2</v>
@@ -1539,28 +1539,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M3">
-        <v>2.8259546</v>
+        <v>5.6519092</v>
       </c>
       <c r="N3">
-        <v>569.3822086653062</v>
+        <v>566.5562540653062</v>
       </c>
       <c r="O3">
-        <v>170.8146625995919</v>
+        <v>169.9668762195919</v>
       </c>
       <c r="P3">
-        <v>398.5675460657143</v>
+        <v>396.5893778457144</v>
       </c>
       <c r="Q3">
-        <v>1001.767546065714</v>
+        <v>999.7893778457144</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1376961981690576</v>
+        <v>0.1383545747141863</v>
       </c>
       <c r="T3">
-        <v>0.6407409627425109</v>
+        <v>0.6453314553828785</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>202.4831408350673</v>
+        <v>101.2415704175337</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1362916832199025</v>
+        <v>0.1359120302524381</v>
       </c>
       <c r="C4">
-        <v>5615.355789736491</v>
+        <v>5582.352363206501</v>
       </c>
       <c r="D4">
-        <v>5501.519789736491</v>
+        <v>5524.698363206501</v>
       </c>
       <c r="E4">
-        <v>-233.536</v>
+        <v>-177.354</v>
       </c>
       <c r="F4">
-        <v>112.364</v>
+        <v>168.546</v>
       </c>
       <c r="G4">
         <v>226.2</v>
@@ -1621,28 +1621,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M4">
-        <v>5.6519092</v>
+        <v>8.4778638</v>
       </c>
       <c r="N4">
-        <v>566.5562540653062</v>
+        <v>563.7302994653062</v>
       </c>
       <c r="O4">
-        <v>169.9668762195919</v>
+        <v>169.1190898395919</v>
       </c>
       <c r="P4">
-        <v>396.5893778457144</v>
+        <v>394.6112096257143</v>
       </c>
       <c r="Q4">
-        <v>999.7893778457144</v>
+        <v>997.8112096257144</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1383545747141863</v>
+        <v>0.1390265260334413</v>
       </c>
       <c r="T4">
-        <v>0.6453314553828785</v>
+        <v>0.6500165973560371</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.2415704175337</v>
+        <v>67.49438027835576</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1359120302524381</v>
+        <v>0.1355323772849736</v>
       </c>
       <c r="C5">
-        <v>5582.352363206501</v>
+        <v>5549.545071326362</v>
       </c>
       <c r="D5">
-        <v>5524.698363206501</v>
+        <v>5548.073071326362</v>
       </c>
       <c r="E5">
-        <v>-177.354</v>
+        <v>-121.172</v>
       </c>
       <c r="F5">
-        <v>168.546</v>
+        <v>224.728</v>
       </c>
       <c r="G5">
         <v>226.2</v>
@@ -1703,28 +1703,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M5">
-        <v>8.4778638</v>
+        <v>11.3038184</v>
       </c>
       <c r="N5">
-        <v>563.7302994653062</v>
+        <v>560.9043448653063</v>
       </c>
       <c r="O5">
-        <v>169.1190898395919</v>
+        <v>168.2713034595919</v>
       </c>
       <c r="P5">
-        <v>394.6112096257143</v>
+        <v>392.6330414057144</v>
       </c>
       <c r="Q5">
-        <v>997.8112096257144</v>
+        <v>995.8330414057144</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1390265260334413</v>
+        <v>0.1397124763385141</v>
       </c>
       <c r="T5">
-        <v>0.6500165973560371</v>
+        <v>0.6547993464536367</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.49438027835576</v>
+        <v>50.62078520876683</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1355323772849736</v>
+        <v>0.135152724317509</v>
       </c>
       <c r="C6">
-        <v>5549.545071326362</v>
+        <v>5516.936414179954</v>
       </c>
       <c r="D6">
-        <v>5548.073071326362</v>
+        <v>5571.646414179954</v>
       </c>
       <c r="E6">
-        <v>-121.172</v>
+        <v>-64.98999999999995</v>
       </c>
       <c r="F6">
-        <v>224.728</v>
+        <v>280.91</v>
       </c>
       <c r="G6">
         <v>226.2</v>
@@ -1785,28 +1785,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M6">
-        <v>11.3038184</v>
+        <v>14.129773</v>
       </c>
       <c r="N6">
-        <v>560.9043448653063</v>
+        <v>558.0783902653062</v>
       </c>
       <c r="O6">
-        <v>168.2713034595919</v>
+        <v>167.4235170795918</v>
       </c>
       <c r="P6">
-        <v>392.6330414057144</v>
+        <v>390.6548731857143</v>
       </c>
       <c r="Q6">
-        <v>995.8330414057144</v>
+        <v>993.8548731857144</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1397124763385141</v>
+        <v>0.1404128677026411</v>
       </c>
       <c r="T6">
-        <v>0.6547993464536367</v>
+        <v>0.6596827850059225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.62078520876683</v>
+        <v>40.49662816701345</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.135152724317509</v>
+        <v>0.1347730713500445</v>
       </c>
       <c r="C7">
-        <v>5516.936414179954</v>
+        <v>5484.528934523129</v>
       </c>
       <c r="D7">
-        <v>5571.646414179954</v>
+        <v>5595.420934523129</v>
       </c>
       <c r="E7">
-        <v>-64.98999999999995</v>
+        <v>-8.807999999999936</v>
       </c>
       <c r="F7">
-        <v>280.91</v>
+        <v>337.092</v>
       </c>
       <c r="G7">
         <v>226.2</v>
@@ -1867,28 +1867,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M7">
-        <v>14.129773</v>
+        <v>16.9557276</v>
       </c>
       <c r="N7">
-        <v>558.0783902653062</v>
+        <v>555.2524356653062</v>
       </c>
       <c r="O7">
-        <v>167.4235170795918</v>
+        <v>166.5757306995918</v>
       </c>
       <c r="P7">
-        <v>390.6548731857143</v>
+        <v>388.6767049657143</v>
       </c>
       <c r="Q7">
-        <v>993.8548731857144</v>
+        <v>991.8767049657143</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1404128677026411</v>
+        <v>0.1411281610106857</v>
       </c>
       <c r="T7">
-        <v>0.6596827850059225</v>
+        <v>0.6646701265061292</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.49662816701345</v>
+        <v>33.74719013917787</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1347730713500445</v>
+        <v>0.1343934183825801</v>
       </c>
       <c r="C8">
-        <v>5484.528934523129</v>
+        <v>5452.325218698043</v>
       </c>
       <c r="D8">
-        <v>5595.420934523129</v>
+        <v>5619.399218698044</v>
       </c>
       <c r="E8">
-        <v>-8.807999999999993</v>
+        <v>47.37399999999997</v>
       </c>
       <c r="F8">
-        <v>337.092</v>
+        <v>393.2739999999999</v>
       </c>
       <c r="G8">
         <v>226.2</v>
@@ -1949,28 +1949,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M8">
-        <v>16.9557276</v>
+        <v>19.7816822</v>
       </c>
       <c r="N8">
-        <v>555.2524356653062</v>
+        <v>552.4264810653062</v>
       </c>
       <c r="O8">
-        <v>166.5757306995918</v>
+        <v>165.7279443195919</v>
       </c>
       <c r="P8">
-        <v>388.6767049657143</v>
+        <v>386.6985367457144</v>
       </c>
       <c r="Q8">
-        <v>991.8767049657143</v>
+        <v>989.8985367457144</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1411281610106857</v>
+        <v>0.1418588369705162</v>
       </c>
       <c r="T8">
-        <v>0.6646701265061292</v>
+        <v>0.6697647226622545</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.74719013917787</v>
+        <v>28.92616297643819</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1343934183825801</v>
+        <v>0.1340137654151156</v>
       </c>
       <c r="C9">
-        <v>5452.325218698043</v>
+        <v>5420.327897571082</v>
       </c>
       <c r="D9">
-        <v>5619.399218698044</v>
+        <v>5643.583897571082</v>
       </c>
       <c r="E9">
-        <v>47.37400000000002</v>
+        <v>103.556</v>
       </c>
       <c r="F9">
-        <v>393.274</v>
+        <v>449.456</v>
       </c>
       <c r="G9">
         <v>226.2</v>
@@ -2031,28 +2031,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M9">
-        <v>19.7816822</v>
+        <v>22.6076368</v>
       </c>
       <c r="N9">
-        <v>552.4264810653062</v>
+        <v>549.6005264653062</v>
       </c>
       <c r="O9">
-        <v>165.7279443195919</v>
+        <v>164.8801579395918</v>
       </c>
       <c r="P9">
-        <v>386.6985367457144</v>
+        <v>384.7203685257143</v>
       </c>
       <c r="Q9">
-        <v>989.8985367457144</v>
+        <v>987.9203685257144</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1418588369705162</v>
+        <v>0.142605397190343</v>
       </c>
       <c r="T9">
-        <v>0.6697647226622545</v>
+        <v>0.6749700709087303</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.92616297643819</v>
+        <v>25.31039260438341</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1340137654151156</v>
+        <v>0.1336341124476511</v>
       </c>
       <c r="C10">
-        <v>5420.327897571082</v>
+        <v>5388.539647495121</v>
       </c>
       <c r="D10">
-        <v>5643.583897571082</v>
+        <v>5667.977647495121</v>
       </c>
       <c r="E10">
-        <v>103.556</v>
+        <v>159.738</v>
       </c>
       <c r="F10">
-        <v>449.456</v>
+        <v>505.638</v>
       </c>
       <c r="G10">
         <v>226.2</v>
@@ -2113,28 +2113,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M10">
-        <v>22.6076368</v>
+        <v>25.4335914</v>
       </c>
       <c r="N10">
-        <v>549.6005264653062</v>
+        <v>546.7745718653063</v>
       </c>
       <c r="O10">
-        <v>164.8801579395918</v>
+        <v>164.0323715595919</v>
       </c>
       <c r="P10">
-        <v>384.7203685257143</v>
+        <v>382.7422003057144</v>
       </c>
       <c r="Q10">
-        <v>987.9203685257144</v>
+        <v>985.9422003057144</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.142605397190343</v>
+        <v>0.1433683653270891</v>
       </c>
       <c r="T10">
-        <v>0.6749700709087303</v>
+        <v>0.6802898224133703</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.31039260438341</v>
+        <v>22.49812675945192</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1336341124476511</v>
+        <v>0.1332544594801866</v>
       </c>
       <c r="C11">
-        <v>5388.539647495121</v>
+        <v>5356.963191296824</v>
       </c>
       <c r="D11">
-        <v>5667.977647495121</v>
+        <v>5692.583191296824</v>
       </c>
       <c r="E11">
-        <v>159.738</v>
+        <v>215.92</v>
       </c>
       <c r="F11">
-        <v>505.638</v>
+        <v>561.8199999999999</v>
       </c>
       <c r="G11">
         <v>226.2</v>
@@ -2195,28 +2195,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M11">
-        <v>25.4335914</v>
+        <v>28.259546</v>
       </c>
       <c r="N11">
-        <v>546.7745718653063</v>
+        <v>543.9486172653062</v>
       </c>
       <c r="O11">
-        <v>164.0323715595919</v>
+        <v>163.1845851795919</v>
       </c>
       <c r="P11">
-        <v>382.7422003057144</v>
+        <v>380.7640320857143</v>
       </c>
       <c r="Q11">
-        <v>985.9422003057144</v>
+        <v>983.9640320857144</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1433683653270891</v>
+        <v>0.1441482883113184</v>
       </c>
       <c r="T11">
-        <v>0.6802898224133703</v>
+        <v>0.6857277906181134</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.49812675945192</v>
+        <v>20.24831408350673</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1332544594801866</v>
+        <v>0.1328748065127221</v>
       </c>
       <c r="C12">
-        <v>5356.963191296824</v>
+        <v>5325.601299289812</v>
       </c>
       <c r="D12">
-        <v>5692.583191296824</v>
+        <v>5717.403299289812</v>
       </c>
       <c r="E12">
-        <v>215.9200000000001</v>
+        <v>272.102</v>
       </c>
       <c r="F12">
-        <v>561.8200000000001</v>
+        <v>618.002</v>
       </c>
       <c r="G12">
         <v>226.2</v>
@@ -2277,28 +2277,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M12">
-        <v>28.259546</v>
+        <v>31.0855006</v>
       </c>
       <c r="N12">
-        <v>543.9486172653062</v>
+        <v>541.1226626653062</v>
       </c>
       <c r="O12">
-        <v>163.1845851795919</v>
+        <v>162.3367987995918</v>
       </c>
       <c r="P12">
-        <v>380.7640320857143</v>
+        <v>378.7858638657143</v>
       </c>
       <c r="Q12">
-        <v>983.9640320857144</v>
+        <v>981.9858638657144</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1441482883113184</v>
+        <v>0.1449457376547439</v>
       </c>
       <c r="T12">
-        <v>0.6857277906181134</v>
+        <v>0.6912879603555475</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.24831408350673</v>
+        <v>18.40755825773339</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1328748065127221</v>
+        <v>0.1324951535452576</v>
       </c>
       <c r="C13">
-        <v>5325.601299289812</v>
+        <v>5294.456790314422</v>
       </c>
       <c r="D13">
-        <v>5717.403299289812</v>
+        <v>5742.440790314422</v>
       </c>
       <c r="E13">
-        <v>272.102</v>
+        <v>328.284</v>
       </c>
       <c r="F13">
-        <v>618.002</v>
+        <v>674.184</v>
       </c>
       <c r="G13">
         <v>226.2</v>
@@ -2359,28 +2359,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M13">
-        <v>31.0855006</v>
+        <v>33.9114552</v>
       </c>
       <c r="N13">
-        <v>541.1226626653062</v>
+        <v>538.2967080653062</v>
       </c>
       <c r="O13">
-        <v>162.3367987995918</v>
+        <v>161.4890124195919</v>
       </c>
       <c r="P13">
-        <v>378.7858638657143</v>
+        <v>376.8076956457144</v>
       </c>
       <c r="Q13">
-        <v>981.9858638657144</v>
+        <v>980.0076956457144</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1449457376547439</v>
+        <v>0.1457613108468837</v>
       </c>
       <c r="T13">
-        <v>0.6912879603555475</v>
+        <v>0.6969744975870141</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.40755825773339</v>
+        <v>16.87359506958894</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1324951535452576</v>
+        <v>0.1321155005777931</v>
       </c>
       <c r="C14">
-        <v>5294.456790314422</v>
+        <v>5263.532532804919</v>
       </c>
       <c r="D14">
-        <v>5742.440790314422</v>
+        <v>5767.69853280492</v>
       </c>
       <c r="E14">
-        <v>328.284</v>
+        <v>384.466</v>
       </c>
       <c r="F14">
-        <v>674.184</v>
+        <v>730.366</v>
       </c>
       <c r="G14">
         <v>226.2</v>
@@ -2441,28 +2441,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M14">
-        <v>33.9114552</v>
+        <v>36.73740979999999</v>
       </c>
       <c r="N14">
-        <v>538.2967080653062</v>
+        <v>535.4707534653062</v>
       </c>
       <c r="O14">
-        <v>161.4890124195919</v>
+        <v>160.6412260395919</v>
       </c>
       <c r="P14">
-        <v>376.8076956457144</v>
+        <v>374.8295274257143</v>
       </c>
       <c r="Q14">
-        <v>980.0076956457144</v>
+        <v>978.0295274257144</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1457613108468837</v>
+        <v>0.146595632848038</v>
       </c>
       <c r="T14">
-        <v>0.6969744975870141</v>
+        <v>0.7027917598123075</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.87359506958894</v>
+        <v>15.5756262180821</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1321155005777931</v>
+        <v>0.1317358476103286</v>
       </c>
       <c r="C15">
-        <v>5263.532532804919</v>
+        <v>5232.831445884976</v>
       </c>
       <c r="D15">
-        <v>5767.69853280492</v>
+        <v>5793.179445884976</v>
       </c>
       <c r="E15">
-        <v>384.466</v>
+        <v>440.648</v>
       </c>
       <c r="F15">
-        <v>730.366</v>
+        <v>786.548</v>
       </c>
       <c r="G15">
         <v>226.2</v>
@@ -2523,28 +2523,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M15">
-        <v>36.73740979999999</v>
+        <v>39.5633644</v>
       </c>
       <c r="N15">
-        <v>535.4707534653062</v>
+        <v>532.6447988653063</v>
       </c>
       <c r="O15">
-        <v>160.6412260395919</v>
+        <v>159.7934396595919</v>
       </c>
       <c r="P15">
-        <v>374.8295274257143</v>
+        <v>372.8513592057144</v>
       </c>
       <c r="Q15">
-        <v>978.0295274257144</v>
+        <v>976.0513592057144</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.146595632848038</v>
+        <v>0.1474493576864286</v>
       </c>
       <c r="T15">
-        <v>0.7027917598123075</v>
+        <v>0.708744307205631</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.5756262180821</v>
+        <v>14.46308148821909</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1317358476103286</v>
+        <v>0.1313561946428641</v>
       </c>
       <c r="C16">
-        <v>5232.831445884976</v>
+        <v>5202.356500492364</v>
       </c>
       <c r="D16">
-        <v>5793.179445884976</v>
+        <v>5818.886500492365</v>
       </c>
       <c r="E16">
-        <v>440.648</v>
+        <v>496.8300000000002</v>
       </c>
       <c r="F16">
-        <v>786.548</v>
+        <v>842.7300000000001</v>
       </c>
       <c r="G16">
         <v>226.2</v>
@@ -2605,28 +2605,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M16">
-        <v>39.5633644</v>
+        <v>42.38931900000001</v>
       </c>
       <c r="N16">
-        <v>532.6447988653063</v>
+        <v>529.8188442653062</v>
       </c>
       <c r="O16">
-        <v>159.7934396595919</v>
+        <v>158.9456532795919</v>
       </c>
       <c r="P16">
-        <v>372.8513592057144</v>
+        <v>370.8731909857144</v>
       </c>
       <c r="Q16">
-        <v>976.0513592057144</v>
+        <v>974.0731909857144</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1474493576864286</v>
+        <v>0.1483231701680754</v>
       </c>
       <c r="T16">
-        <v>0.708744307205631</v>
+        <v>0.714836914537621</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.46308148821909</v>
+        <v>13.49887605567115</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1313561946428641</v>
+        <v>0.1309765416753996</v>
       </c>
       <c r="C17">
-        <v>5202.356500492365</v>
+        <v>5172.110720533676</v>
       </c>
       <c r="D17">
-        <v>5818.886500492365</v>
+        <v>5844.822720533676</v>
       </c>
       <c r="E17">
-        <v>496.8299999999999</v>
+        <v>553.0120000000001</v>
       </c>
       <c r="F17">
-        <v>842.7299999999999</v>
+        <v>898.912</v>
       </c>
       <c r="G17">
         <v>226.2</v>
@@ -2687,28 +2687,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M17">
-        <v>42.38931899999999</v>
+        <v>45.2152736</v>
       </c>
       <c r="N17">
-        <v>529.8188442653062</v>
+        <v>526.9928896653062</v>
       </c>
       <c r="O17">
-        <v>158.9456532795919</v>
+        <v>158.0978668995918</v>
       </c>
       <c r="P17">
-        <v>370.8731909857144</v>
+        <v>368.8950227657143</v>
       </c>
       <c r="Q17">
-        <v>974.0731909857144</v>
+        <v>972.0950227657144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1483231701680754</v>
+        <v>0.1492177877088091</v>
       </c>
       <c r="T17">
-        <v>0.714836914537621</v>
+        <v>0.7210745839489441</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.49887605567115</v>
+        <v>12.6551963021917</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1309765416753996</v>
+        <v>0.1305968887079351</v>
       </c>
       <c r="C18">
-        <v>5172.110720533676</v>
+        <v>5142.097184070086</v>
       </c>
       <c r="D18">
-        <v>5844.822720533676</v>
+        <v>5870.991184070086</v>
       </c>
       <c r="E18">
-        <v>553.0120000000001</v>
+        <v>609.1940000000001</v>
       </c>
       <c r="F18">
-        <v>898.912</v>
+        <v>955.0940000000001</v>
       </c>
       <c r="G18">
         <v>226.2</v>
@@ -2769,28 +2769,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M18">
-        <v>45.2152736</v>
+        <v>48.0412282</v>
       </c>
       <c r="N18">
-        <v>526.9928896653062</v>
+        <v>524.1669350653062</v>
       </c>
       <c r="O18">
-        <v>158.0978668995918</v>
+        <v>157.2500805195919</v>
       </c>
       <c r="P18">
-        <v>368.8950227657143</v>
+        <v>366.9168545457144</v>
       </c>
       <c r="Q18">
-        <v>972.0950227657144</v>
+        <v>970.1168545457144</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1492177877088091</v>
+        <v>0.150133962298717</v>
       </c>
       <c r="T18">
-        <v>0.7210745839489441</v>
+        <v>0.727462558647287</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.6551963021917</v>
+        <v>11.91077299029808</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1305968887079351</v>
+        <v>0.1302172357404706</v>
       </c>
       <c r="C19">
-        <v>5142.097184070086</v>
+        <v>5112.319024535115</v>
       </c>
       <c r="D19">
-        <v>5870.991184070086</v>
+        <v>5897.395024535115</v>
       </c>
       <c r="E19">
-        <v>609.1940000000001</v>
+        <v>665.3760000000001</v>
       </c>
       <c r="F19">
-        <v>955.0940000000001</v>
+        <v>1011.276</v>
       </c>
       <c r="G19">
         <v>226.2</v>
@@ -2851,28 +2851,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M19">
-        <v>48.0412282</v>
+        <v>50.8671828</v>
       </c>
       <c r="N19">
-        <v>524.1669350653062</v>
+        <v>521.3409804653062</v>
       </c>
       <c r="O19">
-        <v>157.2500805195919</v>
+        <v>156.4022941395918</v>
       </c>
       <c r="P19">
-        <v>366.9168545457144</v>
+        <v>364.9386863257143</v>
       </c>
       <c r="Q19">
-        <v>970.1168545457144</v>
+        <v>968.1386863257144</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.150133962298717</v>
+        <v>0.15107248261033</v>
       </c>
       <c r="T19">
-        <v>0.727462558647287</v>
+        <v>0.734006337606565</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.91077299029808</v>
+        <v>11.24906337972596</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1302172357404706</v>
+        <v>0.1298375827730061</v>
       </c>
       <c r="C20">
-        <v>5112.319024535112</v>
+        <v>5082.779431985395</v>
       </c>
       <c r="D20">
-        <v>5897.395024535112</v>
+        <v>5924.037431985395</v>
       </c>
       <c r="E20">
-        <v>665.376</v>
+        <v>721.5580000000001</v>
       </c>
       <c r="F20">
-        <v>1011.276</v>
+        <v>1067.458</v>
       </c>
       <c r="G20">
         <v>226.2</v>
@@ -2933,28 +2933,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M20">
-        <v>50.86718279999999</v>
+        <v>53.6931374</v>
       </c>
       <c r="N20">
-        <v>521.3409804653062</v>
+        <v>518.5150258653063</v>
       </c>
       <c r="O20">
-        <v>156.4022941395918</v>
+        <v>155.5545077595919</v>
       </c>
       <c r="P20">
-        <v>364.9386863257143</v>
+        <v>362.9605181057144</v>
       </c>
       <c r="Q20">
-        <v>968.1386863257144</v>
+        <v>966.1605181057145</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.15107248261033</v>
+        <v>0.1520341762629705</v>
       </c>
       <c r="T20">
-        <v>0.734006337606565</v>
+        <v>0.740711691354961</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.24906337972596</v>
+        <v>10.65700741237196</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1298375827730061</v>
+        <v>0.1294579298055417</v>
       </c>
       <c r="C21">
-        <v>5082.779431985395</v>
+        <v>5053.48165438549</v>
       </c>
       <c r="D21">
-        <v>5924.037431985395</v>
+        <v>5950.921654385491</v>
       </c>
       <c r="E21">
-        <v>721.5580000000001</v>
+        <v>777.7400000000001</v>
       </c>
       <c r="F21">
-        <v>1067.458</v>
+        <v>1123.64</v>
       </c>
       <c r="G21">
         <v>226.2</v>
@@ -3015,28 +3015,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M21">
-        <v>53.6931374</v>
+        <v>56.519092</v>
       </c>
       <c r="N21">
-        <v>518.5150258653063</v>
+        <v>515.6890712653062</v>
       </c>
       <c r="O21">
-        <v>155.5545077595919</v>
+        <v>154.7067213795919</v>
       </c>
       <c r="P21">
-        <v>362.9605181057144</v>
+        <v>360.9823498857144</v>
       </c>
       <c r="Q21">
-        <v>966.1605181057145</v>
+        <v>964.1823498857144</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1520341762629705</v>
+        <v>0.1530199122569271</v>
       </c>
       <c r="T21">
-        <v>0.740711691354961</v>
+        <v>0.747584678947067</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.65700741237196</v>
+        <v>10.12415704175336</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1294579298055417</v>
+        <v>0.1290782768380772</v>
       </c>
       <c r="C22">
-        <v>5053.48165438549</v>
+        <v>5024.428998927875</v>
       </c>
       <c r="D22">
-        <v>5950.921654385491</v>
+        <v>5978.050998927875</v>
       </c>
       <c r="E22">
-        <v>777.7400000000001</v>
+        <v>833.9220000000001</v>
       </c>
       <c r="F22">
-        <v>1123.64</v>
+        <v>1179.822</v>
       </c>
       <c r="G22">
         <v>226.2</v>
@@ -3097,28 +3097,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M22">
-        <v>56.519092</v>
+        <v>59.3450466</v>
       </c>
       <c r="N22">
-        <v>515.6890712653062</v>
+        <v>512.8631166653062</v>
       </c>
       <c r="O22">
-        <v>154.7067213795919</v>
+        <v>153.8589349995918</v>
       </c>
       <c r="P22">
-        <v>360.9823498857144</v>
+        <v>359.0041816657143</v>
       </c>
       <c r="Q22">
-        <v>964.1823498857144</v>
+        <v>962.2041816657144</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1530199122569271</v>
+        <v>0.1540306035925027</v>
       </c>
       <c r="T22">
-        <v>0.747584678947067</v>
+        <v>0.7546316662250491</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.12415704175336</v>
+        <v>9.642054325479393</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1290782768380771</v>
+        <v>0.1286986238706126</v>
       </c>
       <c r="C23">
-        <v>5024.428998927877</v>
+        <v>4995.62483338915</v>
       </c>
       <c r="D23">
-        <v>5978.050998927877</v>
+        <v>6005.42883338915</v>
       </c>
       <c r="E23">
-        <v>833.9219999999999</v>
+        <v>890.1039999999999</v>
       </c>
       <c r="F23">
-        <v>1179.822</v>
+        <v>1236.004</v>
       </c>
       <c r="G23">
         <v>226.2</v>
@@ -3179,28 +3179,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M23">
-        <v>59.34504659999999</v>
+        <v>62.17100119999999</v>
       </c>
       <c r="N23">
-        <v>512.8631166653063</v>
+        <v>510.0371620653062</v>
       </c>
       <c r="O23">
-        <v>153.8589349995919</v>
+        <v>153.0111486195919</v>
       </c>
       <c r="P23">
-        <v>359.0041816657144</v>
+        <v>357.0260134457144</v>
       </c>
       <c r="Q23">
-        <v>962.2041816657145</v>
+        <v>960.2260134457144</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1540306035925027</v>
+        <v>0.155067210090529</v>
       </c>
       <c r="T23">
-        <v>0.754631666225049</v>
+        <v>0.7618593454845178</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.642054325479396</v>
+        <v>9.203779128866696</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1286986238706126</v>
+        <v>0.1283189709031482</v>
       </c>
       <c r="C24">
-        <v>4995.62483338915</v>
+        <v>4967.072587523735</v>
       </c>
       <c r="D24">
-        <v>6005.42883338915</v>
+        <v>6033.058587523735</v>
       </c>
       <c r="E24">
-        <v>890.1039999999999</v>
+        <v>946.2859999999999</v>
       </c>
       <c r="F24">
-        <v>1236.004</v>
+        <v>1292.186</v>
       </c>
       <c r="G24">
         <v>226.2</v>
@@ -3261,28 +3261,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M24">
-        <v>62.17100119999999</v>
+        <v>64.99695579999999</v>
       </c>
       <c r="N24">
-        <v>510.0371620653062</v>
+        <v>507.2112074653062</v>
       </c>
       <c r="O24">
-        <v>153.0111486195919</v>
+        <v>152.1633622395919</v>
       </c>
       <c r="P24">
-        <v>357.0260134457144</v>
+        <v>355.0478452257144</v>
       </c>
       <c r="Q24">
-        <v>960.2260134457144</v>
+        <v>958.2478452257144</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.155067210090529</v>
+        <v>0.15613074143266</v>
       </c>
       <c r="T24">
-        <v>0.7618593454845178</v>
+        <v>0.7692747566728039</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.203779128866696</v>
+        <v>8.803614818915968</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1283189709031482</v>
+        <v>0.1281913179356837</v>
       </c>
       <c r="C25">
-        <v>4967.072587523735</v>
+        <v>4920.237905310128</v>
       </c>
       <c r="D25">
-        <v>6033.058587523735</v>
+        <v>6042.405905310128</v>
       </c>
       <c r="E25">
-        <v>946.2859999999999</v>
+        <v>1002.468</v>
       </c>
       <c r="F25">
-        <v>1292.186</v>
+        <v>1348.368</v>
       </c>
       <c r="G25">
         <v>226.2</v>
@@ -3343,45 +3343,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M25">
-        <v>64.99695579999999</v>
+        <v>69.8454624</v>
       </c>
       <c r="N25">
-        <v>507.2112074653062</v>
+        <v>502.3627008653062</v>
       </c>
       <c r="O25">
-        <v>152.1633622395919</v>
+        <v>150.7088102595919</v>
       </c>
       <c r="P25">
-        <v>355.0478452257144</v>
+        <v>351.6538906057144</v>
       </c>
       <c r="Q25">
-        <v>958.2478452257144</v>
+        <v>954.8538906057145</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.15613074143266</v>
+        <v>0.157222260441689</v>
       </c>
       <c r="T25">
-        <v>0.7692747566728039</v>
+        <v>0.7768853102607819</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>8.803614818915968</v>
+        <v>8.192488725871851</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1281913179356837</v>
+        <v>0.1278221649682192</v>
       </c>
       <c r="C26">
-        <v>4920.237905310129</v>
+        <v>4891.250652869333</v>
       </c>
       <c r="D26">
-        <v>6042.405905310128</v>
+        <v>6069.600652869333</v>
       </c>
       <c r="E26">
-        <v>1002.468</v>
+        <v>1058.65</v>
       </c>
       <c r="F26">
-        <v>1348.368</v>
+        <v>1404.55</v>
       </c>
       <c r="G26">
         <v>226.2</v>
@@ -3425,28 +3425,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M26">
-        <v>69.84546239999999</v>
+        <v>72.75569</v>
       </c>
       <c r="N26">
-        <v>502.3627008653062</v>
+        <v>499.4524732653062</v>
       </c>
       <c r="O26">
-        <v>150.7088102595919</v>
+        <v>149.8357419795919</v>
       </c>
       <c r="P26">
-        <v>351.6538906057144</v>
+        <v>349.6167312857143</v>
       </c>
       <c r="Q26">
-        <v>954.8538906057145</v>
+        <v>952.8167312857144</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.157222260441689</v>
+        <v>0.1583428866242922</v>
       </c>
       <c r="T26">
-        <v>0.7768853102607819</v>
+        <v>0.7846988119444391</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.192488725871851</v>
+        <v>7.864789176836975</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1278221649682192</v>
+        <v>0.1274530120007547</v>
       </c>
       <c r="C27">
-        <v>4891.250652869333</v>
+        <v>4862.509295136277</v>
       </c>
       <c r="D27">
-        <v>6069.600652869333</v>
+        <v>6097.041295136277</v>
       </c>
       <c r="E27">
-        <v>1058.65</v>
+        <v>1114.832</v>
       </c>
       <c r="F27">
-        <v>1404.55</v>
+        <v>1460.732</v>
       </c>
       <c r="G27">
         <v>226.2</v>
@@ -3507,28 +3507,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M27">
-        <v>72.75569</v>
+        <v>75.6659176</v>
       </c>
       <c r="N27">
-        <v>499.4524732653062</v>
+        <v>496.5422456653062</v>
       </c>
       <c r="O27">
-        <v>149.8357419795919</v>
+        <v>148.9626736995918</v>
       </c>
       <c r="P27">
-        <v>349.6167312857143</v>
+        <v>347.5795719657144</v>
       </c>
       <c r="Q27">
-        <v>952.8167312857144</v>
+        <v>950.7795719657145</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1583428866242922</v>
+        <v>0.1594938000010198</v>
       </c>
       <c r="T27">
-        <v>0.7846988119444391</v>
+        <v>0.7927234893492763</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.864789176836975</v>
+        <v>7.562297285420169</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1274530120007547</v>
+        <v>0.1270838590332902</v>
       </c>
       <c r="C28">
-        <v>4862.509295136277</v>
+        <v>4834.017182324476</v>
       </c>
       <c r="D28">
-        <v>6097.041295136277</v>
+        <v>6124.731182324476</v>
       </c>
       <c r="E28">
-        <v>1114.832</v>
+        <v>1171.014</v>
       </c>
       <c r="F28">
-        <v>1460.732</v>
+        <v>1516.914</v>
       </c>
       <c r="G28">
         <v>226.2</v>
@@ -3589,28 +3589,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M28">
-        <v>75.6659176</v>
+        <v>78.5761452</v>
       </c>
       <c r="N28">
-        <v>496.5422456653062</v>
+        <v>493.6320180653062</v>
       </c>
       <c r="O28">
-        <v>148.9626736995918</v>
+        <v>148.0896054195919</v>
       </c>
       <c r="P28">
-        <v>347.5795719657144</v>
+        <v>345.5424126457144</v>
       </c>
       <c r="Q28">
-        <v>950.7795719657145</v>
+        <v>948.7424126457145</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1594938000010198</v>
+        <v>0.1606762452510825</v>
       </c>
       <c r="T28">
-        <v>0.7927234893492763</v>
+        <v>0.8009680209295886</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.562297285420169</v>
+        <v>7.282212200774978</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1270838590332902</v>
+        <v>0.1267147060658257</v>
       </c>
       <c r="C29">
-        <v>4834.017182324476</v>
+        <v>4805.777725785465</v>
       </c>
       <c r="D29">
-        <v>6124.731182324476</v>
+        <v>6152.673725785465</v>
       </c>
       <c r="E29">
-        <v>1171.014</v>
+        <v>1227.196</v>
       </c>
       <c r="F29">
-        <v>1516.914</v>
+        <v>1573.096</v>
       </c>
       <c r="G29">
         <v>226.2</v>
@@ -3671,28 +3671,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M29">
-        <v>78.5761452</v>
+        <v>81.4863728</v>
       </c>
       <c r="N29">
-        <v>493.6320180653062</v>
+        <v>490.7217904653062</v>
       </c>
       <c r="O29">
-        <v>148.0896054195919</v>
+        <v>147.2165371395918</v>
       </c>
       <c r="P29">
-        <v>345.5424126457144</v>
+        <v>343.5052533257143</v>
       </c>
       <c r="Q29">
-        <v>948.7424126457145</v>
+        <v>946.7052533257144</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1606762452510825</v>
+        <v>0.1618915362025357</v>
       </c>
       <c r="T29">
-        <v>0.8009680209295886</v>
+        <v>0.8094415672760205</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.282212200774978</v>
+        <v>7.022133193604443</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1267147060658257</v>
+        <v>0.1263455530983612</v>
       </c>
       <c r="C30">
-        <v>4805.777725785465</v>
+        <v>4777.794399409825</v>
       </c>
       <c r="D30">
-        <v>6152.673725785465</v>
+        <v>6180.872399409825</v>
       </c>
       <c r="E30">
-        <v>1227.196</v>
+        <v>1283.378</v>
       </c>
       <c r="F30">
-        <v>1573.096</v>
+        <v>1629.278</v>
       </c>
       <c r="G30">
         <v>226.2</v>
@@ -3753,28 +3753,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M30">
-        <v>81.4863728</v>
+        <v>84.39660040000001</v>
       </c>
       <c r="N30">
-        <v>490.7217904653062</v>
+        <v>487.8115628653062</v>
       </c>
       <c r="O30">
-        <v>147.2165371395918</v>
+        <v>146.3434688595919</v>
       </c>
       <c r="P30">
-        <v>343.5052533257143</v>
+        <v>341.4680940057143</v>
       </c>
       <c r="Q30">
-        <v>946.7052533257144</v>
+        <v>944.6680940057144</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1618915362025357</v>
+        <v>0.1631410607019172</v>
       </c>
       <c r="T30">
-        <v>0.8094415672760205</v>
+        <v>0.818153805068831</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.022133193604443</v>
+        <v>6.779990669687048</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1263455530983612</v>
+        <v>0.1263334001308967</v>
       </c>
       <c r="C31">
-        <v>4777.794399409826</v>
+        <v>4722.545129693782</v>
       </c>
       <c r="D31">
-        <v>6180.872399409825</v>
+        <v>6181.805129693782</v>
       </c>
       <c r="E31">
-        <v>1283.378</v>
+        <v>1339.56</v>
       </c>
       <c r="F31">
-        <v>1629.278</v>
+        <v>1685.46</v>
       </c>
       <c r="G31">
         <v>226.2</v>
@@ -3835,45 +3835,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M31">
-        <v>84.39660039999998</v>
+        <v>90.17210999999999</v>
       </c>
       <c r="N31">
-        <v>487.8115628653062</v>
+        <v>482.0360532653062</v>
       </c>
       <c r="O31">
-        <v>146.3434688595919</v>
+        <v>144.6108159795919</v>
       </c>
       <c r="P31">
-        <v>341.4680940057143</v>
+        <v>337.4252372857144</v>
       </c>
       <c r="Q31">
-        <v>944.6680940057144</v>
+        <v>940.6252372857144</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1631410607019172</v>
+        <v>0.164426285901281</v>
       </c>
       <c r="T31">
-        <v>0.818153805068831</v>
+        <v>0.8271149639414359</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.77999066968705</v>
+        <v>6.345733323366907</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1263334001308967</v>
+        <v>0.1259761471634322</v>
       </c>
       <c r="C32">
-        <v>4722.545129693782</v>
+        <v>4693.9083324131</v>
       </c>
       <c r="D32">
-        <v>6181.805129693782</v>
+        <v>6209.3503324131</v>
       </c>
       <c r="E32">
-        <v>1339.56</v>
+        <v>1395.742</v>
       </c>
       <c r="F32">
-        <v>1685.46</v>
+        <v>1741.642</v>
       </c>
       <c r="G32">
         <v>226.2</v>
@@ -3917,28 +3917,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M32">
-        <v>90.17210999999999</v>
+        <v>93.17784699999999</v>
       </c>
       <c r="N32">
-        <v>482.0360532653062</v>
+        <v>479.0303162653062</v>
       </c>
       <c r="O32">
-        <v>144.6108159795919</v>
+        <v>143.7090948795919</v>
       </c>
       <c r="P32">
-        <v>337.4252372857144</v>
+        <v>335.3212213857144</v>
       </c>
       <c r="Q32">
-        <v>940.6252372857144</v>
+        <v>938.5212213857144</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.164426285901281</v>
+        <v>0.1657487640049742</v>
       </c>
       <c r="T32">
-        <v>0.8271149639414359</v>
+        <v>0.8363358665494786</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.345733323366907</v>
+        <v>6.141032248419587</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1259761471634322</v>
+        <v>0.1256188941959677</v>
       </c>
       <c r="C33">
-        <v>4693.9083324131</v>
+        <v>4665.51810846596</v>
       </c>
       <c r="D33">
-        <v>6209.3503324131</v>
+        <v>6237.142108465961</v>
       </c>
       <c r="E33">
-        <v>1395.742</v>
+        <v>1451.924</v>
       </c>
       <c r="F33">
-        <v>1741.642</v>
+        <v>1797.824</v>
       </c>
       <c r="G33">
         <v>226.2</v>
@@ -3999,28 +3999,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M33">
-        <v>93.17784699999999</v>
+        <v>96.183584</v>
       </c>
       <c r="N33">
-        <v>479.0303162653062</v>
+        <v>476.0245792653062</v>
       </c>
       <c r="O33">
-        <v>143.7090948795919</v>
+        <v>142.8073737795919</v>
       </c>
       <c r="P33">
-        <v>335.3212213857144</v>
+        <v>333.2172054857143</v>
       </c>
       <c r="Q33">
-        <v>938.5212213857144</v>
+        <v>936.4172054857144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1657487640049742</v>
+        <v>0.1671101385234819</v>
       </c>
       <c r="T33">
-        <v>0.8363358665494786</v>
+        <v>0.845827972175405</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.141032248419587</v>
+        <v>5.949124990656474</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1256188941959677</v>
+        <v>0.1252616412285032</v>
       </c>
       <c r="C34">
-        <v>4665.51810846596</v>
+        <v>4637.377783572312</v>
       </c>
       <c r="D34">
-        <v>6237.142108465961</v>
+        <v>6265.183783572313</v>
       </c>
       <c r="E34">
-        <v>1451.924</v>
+        <v>1508.106</v>
       </c>
       <c r="F34">
-        <v>1797.824</v>
+        <v>1854.006</v>
       </c>
       <c r="G34">
         <v>226.2</v>
@@ -4081,28 +4081,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M34">
-        <v>96.183584</v>
+        <v>99.18932100000001</v>
       </c>
       <c r="N34">
-        <v>476.0245792653062</v>
+        <v>473.0188422653062</v>
       </c>
       <c r="O34">
-        <v>142.8073737795919</v>
+        <v>141.9056526795919</v>
       </c>
       <c r="P34">
-        <v>333.2172054857143</v>
+        <v>331.1131895857143</v>
       </c>
       <c r="Q34">
-        <v>936.4172054857144</v>
+        <v>934.3131895857143</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1671101385234819</v>
+        <v>0.1685121510873182</v>
       </c>
       <c r="T34">
-        <v>0.845827972175405</v>
+        <v>0.8556034242379262</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.949124990656474</v>
+        <v>5.768848475788096</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1252616412285032</v>
+        <v>0.1249043882610387</v>
       </c>
       <c r="C35">
-        <v>4637.377783572312</v>
+        <v>4609.490743530861</v>
       </c>
       <c r="D35">
-        <v>6265.183783572313</v>
+        <v>6293.478743530861</v>
       </c>
       <c r="E35">
-        <v>1508.106</v>
+        <v>1564.288</v>
       </c>
       <c r="F35">
-        <v>1854.006</v>
+        <v>1910.188</v>
       </c>
       <c r="G35">
         <v>226.2</v>
@@ -4163,28 +4163,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M35">
-        <v>99.18932100000001</v>
+        <v>102.195058</v>
       </c>
       <c r="N35">
-        <v>473.0188422653062</v>
+        <v>470.0131052653062</v>
       </c>
       <c r="O35">
-        <v>141.9056526795919</v>
+        <v>141.0039315795919</v>
       </c>
       <c r="P35">
-        <v>331.1131895857143</v>
+        <v>329.0091736857144</v>
       </c>
       <c r="Q35">
-        <v>934.3131895857143</v>
+        <v>932.2091736857144</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1685121510873182</v>
+        <v>0.1699566488803617</v>
       </c>
       <c r="T35">
-        <v>0.8556034242379262</v>
+        <v>0.8656751021205238</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.768848475788096</v>
+        <v>5.599176461794328</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1249043882610387</v>
+        <v>0.1247431352935742</v>
       </c>
       <c r="C36">
-        <v>4609.490743530861</v>
+        <v>4566.164099722314</v>
       </c>
       <c r="D36">
-        <v>6293.478743530861</v>
+        <v>6306.334099722314</v>
       </c>
       <c r="E36">
-        <v>1564.288</v>
+        <v>1620.47</v>
       </c>
       <c r="F36">
-        <v>1910.188</v>
+        <v>1966.37</v>
       </c>
       <c r="G36">
         <v>226.2</v>
@@ -4245,45 +4245,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M36">
-        <v>102.195058</v>
+        <v>106.773891</v>
       </c>
       <c r="N36">
-        <v>470.0131052653062</v>
+        <v>465.4342722653062</v>
       </c>
       <c r="O36">
-        <v>141.0039315795919</v>
+        <v>139.6302816795919</v>
       </c>
       <c r="P36">
-        <v>329.0091736857144</v>
+        <v>325.8039905857144</v>
       </c>
       <c r="Q36">
-        <v>932.2091736857144</v>
+        <v>929.0039905857144</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1699566488803617</v>
+        <v>0.171445592759345</v>
       </c>
       <c r="T36">
-        <v>0.8656751021205238</v>
+        <v>0.8760566777841243</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>5.599176461794328</v>
+        <v>5.359064448305122</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1247431352935742</v>
+        <v>0.1243914823261097</v>
       </c>
       <c r="C37">
-        <v>4566.164099722314</v>
+        <v>4538.199420917352</v>
       </c>
       <c r="D37">
-        <v>6306.334099722314</v>
+        <v>6334.551420917352</v>
       </c>
       <c r="E37">
-        <v>1620.47</v>
+        <v>1676.652</v>
       </c>
       <c r="F37">
-        <v>1966.37</v>
+        <v>2022.552</v>
       </c>
       <c r="G37">
         <v>226.2</v>
@@ -4327,28 +4327,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M37">
-        <v>106.773891</v>
+        <v>109.8245736</v>
       </c>
       <c r="N37">
-        <v>465.4342722653062</v>
+        <v>462.3835896653062</v>
       </c>
       <c r="O37">
-        <v>139.6302816795919</v>
+        <v>138.7150768995918</v>
       </c>
       <c r="P37">
-        <v>325.8039905857144</v>
+        <v>323.6685127657144</v>
       </c>
       <c r="Q37">
-        <v>929.0039905857144</v>
+        <v>926.8685127657144</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.171445592759345</v>
+        <v>0.1729810661345465</v>
       </c>
       <c r="T37">
-        <v>0.8760566777841243</v>
+        <v>0.8867626776872125</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.359064448305122</v>
+        <v>5.210201546963313</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1243914823261097</v>
+        <v>0.1240398293586452</v>
       </c>
       <c r="C38">
-        <v>4538.199420917351</v>
+        <v>4510.48839053707</v>
       </c>
       <c r="D38">
-        <v>6334.551420917351</v>
+        <v>6363.02239053707</v>
       </c>
       <c r="E38">
-        <v>1676.652</v>
+        <v>1732.834</v>
       </c>
       <c r="F38">
-        <v>2022.552</v>
+        <v>2078.734</v>
       </c>
       <c r="G38">
         <v>226.2</v>
@@ -4409,28 +4409,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M38">
-        <v>109.8245736</v>
+        <v>112.8752562</v>
       </c>
       <c r="N38">
-        <v>462.3835896653062</v>
+        <v>459.3329070653062</v>
       </c>
       <c r="O38">
-        <v>138.7150768995918</v>
+        <v>137.7998721195919</v>
       </c>
       <c r="P38">
-        <v>323.6685127657144</v>
+        <v>321.5330349457143</v>
       </c>
       <c r="Q38">
-        <v>926.8685127657144</v>
+        <v>924.7330349457144</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1729810661345465</v>
+        <v>0.1745652846962623</v>
       </c>
       <c r="T38">
-        <v>0.8867626776872125</v>
+        <v>0.8978085506030969</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.210201546963313</v>
+        <v>5.069385288937278</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1240398293586452</v>
+        <v>0.1236881763911807</v>
       </c>
       <c r="C39">
-        <v>4510.48839053707</v>
+        <v>4483.034444130693</v>
       </c>
       <c r="D39">
-        <v>6363.02239053707</v>
+        <v>6391.750444130694</v>
       </c>
       <c r="E39">
-        <v>1732.834</v>
+        <v>1789.016</v>
       </c>
       <c r="F39">
-        <v>2078.734</v>
+        <v>2134.916</v>
       </c>
       <c r="G39">
         <v>226.2</v>
@@ -4491,28 +4491,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M39">
-        <v>112.8752562</v>
+        <v>115.9259388</v>
       </c>
       <c r="N39">
-        <v>459.3329070653062</v>
+        <v>456.2822244653062</v>
       </c>
       <c r="O39">
-        <v>137.7998721195919</v>
+        <v>136.8846673395919</v>
       </c>
       <c r="P39">
-        <v>321.5330349457143</v>
+        <v>319.3975571257143</v>
       </c>
       <c r="Q39">
-        <v>924.7330349457144</v>
+        <v>922.5975571257144</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1745652846962623</v>
+        <v>0.1762006070825496</v>
       </c>
       <c r="T39">
-        <v>0.8978085506030969</v>
+        <v>0.9092107420001391</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.069385288937278</v>
+        <v>4.935980412912611</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1236881763911807</v>
+        <v>0.1233365234237162</v>
       </c>
       <c r="C40">
-        <v>4483.034444130693</v>
+        <v>4455.841079572704</v>
       </c>
       <c r="D40">
-        <v>6391.750444130694</v>
+        <v>6420.739079572704</v>
       </c>
       <c r="E40">
-        <v>1789.016</v>
+        <v>1845.198</v>
       </c>
       <c r="F40">
-        <v>2134.916</v>
+        <v>2191.098</v>
       </c>
       <c r="G40">
         <v>226.2</v>
@@ -4573,28 +4573,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M40">
-        <v>115.9259388</v>
+        <v>118.9766214</v>
       </c>
       <c r="N40">
-        <v>456.2822244653062</v>
+        <v>453.2315418653062</v>
       </c>
       <c r="O40">
-        <v>136.8846673395919</v>
+        <v>135.9694625595918</v>
       </c>
       <c r="P40">
-        <v>319.3975571257143</v>
+        <v>317.2620793057143</v>
       </c>
       <c r="Q40">
-        <v>922.5975571257144</v>
+        <v>920.4620793057144</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1762006070825496</v>
+        <v>0.1778895465962561</v>
       </c>
       <c r="T40">
-        <v>0.9092107420001391</v>
+        <v>0.9209867757380679</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.935980412912611</v>
+        <v>4.809416812581519</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1233365234237162</v>
+        <v>0.1229848704562518</v>
       </c>
       <c r="C41">
-        <v>4455.841079572704</v>
+        <v>4428.911858482616</v>
       </c>
       <c r="D41">
-        <v>6420.739079572704</v>
+        <v>6449.991858482616</v>
       </c>
       <c r="E41">
-        <v>1845.198</v>
+        <v>1901.38</v>
       </c>
       <c r="F41">
-        <v>2191.098</v>
+        <v>2247.28</v>
       </c>
       <c r="G41">
         <v>226.2</v>
@@ -4655,28 +4655,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M41">
-        <v>118.9766214</v>
+        <v>122.027304</v>
       </c>
       <c r="N41">
-        <v>453.2315418653062</v>
+        <v>450.1808592653062</v>
       </c>
       <c r="O41">
-        <v>135.9694625595918</v>
+        <v>135.0542577795919</v>
       </c>
       <c r="P41">
-        <v>317.2620793057143</v>
+        <v>315.1266014857143</v>
       </c>
       <c r="Q41">
-        <v>920.4620793057144</v>
+        <v>918.3266014857144</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1778895465962561</v>
+        <v>0.1796347840937529</v>
       </c>
       <c r="T41">
-        <v>0.9209867757380679</v>
+        <v>0.9331553439339276</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.809416812581519</v>
+        <v>4.689181392266981</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1229848704562518</v>
+        <v>0.1226332174887873</v>
       </c>
       <c r="C42">
-        <v>4428.911858482616</v>
+        <v>4402.250407683725</v>
       </c>
       <c r="D42">
-        <v>6449.991858482616</v>
+        <v>6479.512407683726</v>
       </c>
       <c r="E42">
-        <v>1901.38</v>
+        <v>1957.562</v>
       </c>
       <c r="F42">
-        <v>2247.28</v>
+        <v>2303.462</v>
       </c>
       <c r="G42">
         <v>226.2</v>
@@ -4737,28 +4737,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M42">
-        <v>122.027304</v>
+        <v>125.0779866</v>
       </c>
       <c r="N42">
-        <v>450.1808592653062</v>
+        <v>447.1301766653062</v>
       </c>
       <c r="O42">
-        <v>135.0542577795919</v>
+        <v>134.1390529995919</v>
       </c>
       <c r="P42">
-        <v>315.1266014857143</v>
+        <v>312.9911236657143</v>
       </c>
       <c r="Q42">
-        <v>918.3266014857144</v>
+        <v>916.1911236657144</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1796347840937529</v>
+        <v>0.1814391821843852</v>
       </c>
       <c r="T42">
-        <v>0.9331553439339276</v>
+        <v>0.9457364059669351</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.689181392266981</v>
+        <v>4.574811114406812</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1226332174887873</v>
+        <v>0.1222815645213228</v>
       </c>
       <c r="C43">
-        <v>4402.250407683725</v>
+        <v>4375.860420702103</v>
       </c>
       <c r="D43">
-        <v>6479.512407683726</v>
+        <v>6509.304420702103</v>
       </c>
       <c r="E43">
-        <v>1957.562</v>
+        <v>2013.744</v>
       </c>
       <c r="F43">
-        <v>2303.462</v>
+        <v>2359.644</v>
       </c>
       <c r="G43">
         <v>226.2</v>
@@ -4819,28 +4819,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M43">
-        <v>125.0779866</v>
+        <v>128.1286692</v>
       </c>
       <c r="N43">
-        <v>447.1301766653062</v>
+        <v>444.0794940653062</v>
       </c>
       <c r="O43">
-        <v>134.1390529995919</v>
+        <v>133.2238482195919</v>
       </c>
       <c r="P43">
-        <v>312.9911236657143</v>
+        <v>310.8556458457143</v>
       </c>
       <c r="Q43">
-        <v>916.1911236657144</v>
+        <v>914.0556458457144</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1814391821843852</v>
+        <v>0.1833058008988324</v>
       </c>
       <c r="T43">
-        <v>0.9457364059669351</v>
+        <v>0.9587512977252187</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.574811114406812</v>
+        <v>4.465887040254268</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1222815645213228</v>
+        <v>0.1219299115538583</v>
       </c>
       <c r="C44">
-        <v>4375.860420702104</v>
+        <v>4349.745659307132</v>
       </c>
       <c r="D44">
-        <v>6509.304420702103</v>
+        <v>6539.371659307132</v>
       </c>
       <c r="E44">
-        <v>2013.744</v>
+        <v>2069.926</v>
       </c>
       <c r="F44">
-        <v>2359.644</v>
+        <v>2415.826</v>
       </c>
       <c r="G44">
         <v>226.2</v>
@@ -4901,28 +4901,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M44">
-        <v>128.1286692</v>
+        <v>131.1793518</v>
       </c>
       <c r="N44">
-        <v>444.0794940653062</v>
+        <v>441.0288114653062</v>
       </c>
       <c r="O44">
-        <v>133.2238482195919</v>
+        <v>132.3086434395919</v>
       </c>
       <c r="P44">
-        <v>310.8556458457143</v>
+        <v>308.7201680257143</v>
       </c>
       <c r="Q44">
-        <v>914.0556458457144</v>
+        <v>911.9201680257144</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1833058008988323</v>
+        <v>0.1852379150067689</v>
       </c>
       <c r="T44">
-        <v>0.9587512977252186</v>
+        <v>0.972222852352214</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.465887040254268</v>
+        <v>4.36202920210882</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1219299115538583</v>
+        <v>0.1215782585863938</v>
       </c>
       <c r="C45">
-        <v>4349.745659307132</v>
+        <v>4323.90995509495</v>
       </c>
       <c r="D45">
-        <v>6539.371659307132</v>
+        <v>6569.71795509495</v>
       </c>
       <c r="E45">
-        <v>2069.926</v>
+        <v>2126.108</v>
       </c>
       <c r="F45">
-        <v>2415.826</v>
+        <v>2472.008</v>
       </c>
       <c r="G45">
         <v>226.2</v>
@@ -4983,28 +4983,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M45">
-        <v>131.1793518</v>
+        <v>134.2300344</v>
       </c>
       <c r="N45">
-        <v>441.0288114653062</v>
+        <v>437.9781288653062</v>
       </c>
       <c r="O45">
-        <v>132.3086434395919</v>
+        <v>131.3934386595919</v>
       </c>
       <c r="P45">
-        <v>308.7201680257143</v>
+        <v>306.5846902057143</v>
       </c>
       <c r="Q45">
-        <v>911.9201680257144</v>
+        <v>909.7846902057144</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1852379150067689</v>
+        <v>0.1872390331899889</v>
       </c>
       <c r="T45">
-        <v>0.972222852352214</v>
+        <v>0.9861755339301734</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.36202920210882</v>
+        <v>4.262892174788165</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1215782585863938</v>
+        <v>0.1215416056189293</v>
       </c>
       <c r="C46">
-        <v>4323.90995509495</v>
+        <v>4270.907180785918</v>
       </c>
       <c r="D46">
-        <v>6569.71795509495</v>
+        <v>6572.897180785918</v>
       </c>
       <c r="E46">
-        <v>2126.108</v>
+        <v>2182.29</v>
       </c>
       <c r="F46">
-        <v>2472.008</v>
+        <v>2528.19</v>
       </c>
       <c r="G46">
         <v>226.2</v>
@@ -5065,45 +5065,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M46">
-        <v>134.2300344</v>
+        <v>139.808907</v>
       </c>
       <c r="N46">
-        <v>437.9781288653062</v>
+        <v>432.3992562653062</v>
       </c>
       <c r="O46">
-        <v>131.3934386595919</v>
+        <v>129.7197768795919</v>
       </c>
       <c r="P46">
-        <v>306.5846902057143</v>
+        <v>302.6794793857143</v>
       </c>
       <c r="Q46">
-        <v>909.7846902057144</v>
+        <v>905.8794793857144</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1872390331899889</v>
+        <v>0.1893129193071442</v>
       </c>
       <c r="T46">
-        <v>0.9861755339301734</v>
+        <v>1.000635585747331</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.262892174788165</v>
+        <v>4.092787616638089</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1215416056189293</v>
+        <v>0.1211969526514648</v>
       </c>
       <c r="C47">
-        <v>4270.907180785918</v>
+        <v>4244.771070421126</v>
       </c>
       <c r="D47">
-        <v>6572.897180785918</v>
+        <v>6602.943070421125</v>
       </c>
       <c r="E47">
-        <v>2182.29</v>
+        <v>2238.472</v>
       </c>
       <c r="F47">
-        <v>2528.19</v>
+        <v>2584.372</v>
       </c>
       <c r="G47">
         <v>226.2</v>
@@ -5147,28 +5147,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M47">
-        <v>139.808907</v>
+        <v>142.9157716</v>
       </c>
       <c r="N47">
-        <v>432.3992562653062</v>
+        <v>429.2923916653062</v>
       </c>
       <c r="O47">
-        <v>129.7197768795919</v>
+        <v>128.7877174995919</v>
       </c>
       <c r="P47">
-        <v>302.6794793857143</v>
+        <v>300.5046741657144</v>
       </c>
       <c r="Q47">
-        <v>905.8794793857144</v>
+        <v>903.7046741657144</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1893129193071442</v>
+        <v>0.1914636160212311</v>
       </c>
       <c r="T47">
-        <v>1.000635585747331</v>
+        <v>1.015631195039199</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.092787616638089</v>
+        <v>4.003813972798131</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1211969526514648</v>
+        <v>0.1208522996840003</v>
       </c>
       <c r="C48">
-        <v>4244.771070421126</v>
+        <v>4218.91091176112</v>
       </c>
       <c r="D48">
-        <v>6602.943070421125</v>
+        <v>6633.26491176112</v>
       </c>
       <c r="E48">
-        <v>2238.472</v>
+        <v>2294.654</v>
       </c>
       <c r="F48">
-        <v>2584.372</v>
+        <v>2640.554</v>
       </c>
       <c r="G48">
         <v>226.2</v>
@@ -5229,28 +5229,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M48">
-        <v>142.9157716</v>
+        <v>146.0226362</v>
       </c>
       <c r="N48">
-        <v>429.2923916653062</v>
+        <v>426.1855270653062</v>
       </c>
       <c r="O48">
-        <v>128.7877174995919</v>
+        <v>127.8556581195919</v>
       </c>
       <c r="P48">
-        <v>300.5046741657144</v>
+        <v>298.3298689457143</v>
       </c>
       <c r="Q48">
-        <v>903.7046741657144</v>
+        <v>901.5298689457144</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1914636160212311</v>
+        <v>0.1936954711018874</v>
       </c>
       <c r="T48">
-        <v>1.015631195039199</v>
+        <v>1.031192676379816</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.003813972798131</v>
+        <v>3.918626441461999</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1208522996840003</v>
+        <v>0.1205076467165358</v>
       </c>
       <c r="C49">
-        <v>4218.91091176112</v>
+        <v>4193.330523996223</v>
       </c>
       <c r="D49">
-        <v>6633.26491176112</v>
+        <v>6663.866523996223</v>
       </c>
       <c r="E49">
-        <v>2294.654</v>
+        <v>2350.836</v>
       </c>
       <c r="F49">
-        <v>2640.554</v>
+        <v>2696.736</v>
       </c>
       <c r="G49">
         <v>226.2</v>
@@ -5311,28 +5311,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M49">
-        <v>146.0226362</v>
+        <v>149.1295008</v>
       </c>
       <c r="N49">
-        <v>426.1855270653062</v>
+        <v>423.0786624653062</v>
       </c>
       <c r="O49">
-        <v>127.8556581195919</v>
+        <v>126.9235987395919</v>
       </c>
       <c r="P49">
-        <v>298.3298689457143</v>
+        <v>296.1550637257143</v>
       </c>
       <c r="Q49">
-        <v>901.5298689457144</v>
+        <v>899.3550637257144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1936954711018874</v>
+        <v>0.1960131667625689</v>
       </c>
       <c r="T49">
-        <v>1.031192676379816</v>
+        <v>1.047352676233534</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.918626441461999</v>
+        <v>3.836988390598208</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1205076467165358</v>
+        <v>0.1201629937490713</v>
       </c>
       <c r="C50">
-        <v>4193.330523996223</v>
+        <v>4168.033797120549</v>
       </c>
       <c r="D50">
-        <v>6663.866523996223</v>
+        <v>6694.751797120549</v>
       </c>
       <c r="E50">
-        <v>2350.836</v>
+        <v>2407.018</v>
       </c>
       <c r="F50">
-        <v>2696.736</v>
+        <v>2752.918</v>
       </c>
       <c r="G50">
         <v>226.2</v>
@@ -5393,28 +5393,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M50">
-        <v>149.1295008</v>
+        <v>152.2363654</v>
       </c>
       <c r="N50">
-        <v>423.0786624653063</v>
+        <v>419.9717978653063</v>
       </c>
       <c r="O50">
-        <v>126.9235987395919</v>
+        <v>125.9915393595919</v>
       </c>
       <c r="P50">
-        <v>296.1550637257144</v>
+        <v>293.9802585057144</v>
       </c>
       <c r="Q50">
-        <v>899.3550637257144</v>
+        <v>897.1802585057144</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1960131667625689</v>
+        <v>0.1984217524491594</v>
       </c>
       <c r="T50">
-        <v>1.047352676233534</v>
+        <v>1.064146401571711</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.836988390598209</v>
+        <v>3.758682505075797</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1201629937490713</v>
+        <v>0.1198183407816068</v>
       </c>
       <c r="C51">
-        <v>4168.033797120549</v>
+        <v>4143.024693580412</v>
       </c>
       <c r="D51">
-        <v>6694.751797120549</v>
+        <v>6725.924693580411</v>
       </c>
       <c r="E51">
-        <v>2407.018</v>
+        <v>2463.2</v>
       </c>
       <c r="F51">
-        <v>2752.918</v>
+        <v>2809.1</v>
       </c>
       <c r="G51">
         <v>226.2</v>
@@ -5475,28 +5475,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M51">
-        <v>152.2363654</v>
+        <v>155.34323</v>
       </c>
       <c r="N51">
-        <v>419.9717978653063</v>
+        <v>416.8649332653062</v>
       </c>
       <c r="O51">
-        <v>125.9915393595919</v>
+        <v>125.0594799795919</v>
       </c>
       <c r="P51">
-        <v>293.9802585057144</v>
+        <v>291.8054532857143</v>
       </c>
       <c r="Q51">
-        <v>897.1802585057144</v>
+        <v>895.0054532857143</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1984217524491594</v>
+        <v>0.2009266815632136</v>
       </c>
       <c r="T51">
-        <v>1.064146401571711</v>
+        <v>1.081611875923416</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.758682505075797</v>
+        <v>3.68350885497428</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1198183407816068</v>
+        <v>0.1194736878141423</v>
       </c>
       <c r="C52">
-        <v>4143.024693580412</v>
+        <v>4118.307249969027</v>
       </c>
       <c r="D52">
-        <v>6725.924693580411</v>
+        <v>6757.389249969027</v>
       </c>
       <c r="E52">
-        <v>2463.2</v>
+        <v>2519.382</v>
       </c>
       <c r="F52">
-        <v>2809.1</v>
+        <v>2865.282</v>
       </c>
       <c r="G52">
         <v>226.2</v>
@@ -5557,28 +5557,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M52">
-        <v>155.34323</v>
+        <v>158.4500946</v>
       </c>
       <c r="N52">
-        <v>416.8649332653062</v>
+        <v>413.7580686653062</v>
       </c>
       <c r="O52">
-        <v>125.0594799795919</v>
+        <v>124.1274205995919</v>
       </c>
       <c r="P52">
-        <v>291.8054532857143</v>
+        <v>289.6306480657144</v>
       </c>
       <c r="Q52">
-        <v>895.0054532857143</v>
+        <v>892.8306480657144</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2009266815632136</v>
+        <v>0.2035338526819231</v>
       </c>
       <c r="T52">
-        <v>1.081611875923416</v>
+        <v>1.099790226779272</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.68350885497428</v>
+        <v>3.611283191151255</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1194736878141423</v>
+        <v>0.1191290348466778</v>
       </c>
       <c r="C53">
-        <v>4118.307249969027</v>
+        <v>4093.88557876899</v>
       </c>
       <c r="D53">
-        <v>6757.389249969027</v>
+        <v>6789.14957876899</v>
       </c>
       <c r="E53">
-        <v>2519.382</v>
+        <v>2575.564</v>
       </c>
       <c r="F53">
-        <v>2865.282</v>
+        <v>2921.464</v>
       </c>
       <c r="G53">
         <v>226.2</v>
@@ -5639,28 +5639,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M53">
-        <v>158.4500946</v>
+        <v>161.5569592</v>
       </c>
       <c r="N53">
-        <v>413.7580686653062</v>
+        <v>410.6512040653062</v>
       </c>
       <c r="O53">
-        <v>124.1274205995919</v>
+        <v>123.1953612195919</v>
       </c>
       <c r="P53">
-        <v>289.6306480657144</v>
+        <v>287.4558428457144</v>
       </c>
       <c r="Q53">
-        <v>892.8306480657144</v>
+        <v>890.6558428457145</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2035338526819231</v>
+        <v>0.2062496559305788</v>
       </c>
       <c r="T53">
-        <v>1.099790226779272</v>
+        <v>1.118726008920788</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.611283191151255</v>
+        <v>3.541835437475269</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1191290348466778</v>
+        <v>0.1187843818792133</v>
       </c>
       <c r="C54">
-        <v>4093.88557876899</v>
+        <v>4069.763870144145</v>
       </c>
       <c r="D54">
-        <v>6789.14957876899</v>
+        <v>6821.209870144145</v>
       </c>
       <c r="E54">
-        <v>2575.564</v>
+        <v>2631.746</v>
       </c>
       <c r="F54">
-        <v>2921.464</v>
+        <v>2977.646</v>
       </c>
       <c r="G54">
         <v>226.2</v>
@@ -5721,28 +5721,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M54">
-        <v>161.5569592</v>
+        <v>164.6638238</v>
       </c>
       <c r="N54">
-        <v>410.6512040653062</v>
+        <v>407.5443394653062</v>
       </c>
       <c r="O54">
-        <v>123.1953612195919</v>
+        <v>122.2633018395918</v>
       </c>
       <c r="P54">
-        <v>287.4558428457144</v>
+        <v>285.2810376257143</v>
       </c>
       <c r="Q54">
-        <v>890.6558428457145</v>
+        <v>888.4810376257144</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2062496559305788</v>
+        <v>0.2090810252749219</v>
       </c>
       <c r="T54">
-        <v>1.118726008920788</v>
+        <v>1.138467569025773</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.541835437475269</v>
+        <v>3.47500835374932</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1187843818792133</v>
+        <v>0.1184397289117488</v>
       </c>
       <c r="C55">
-        <v>4069.763870144145</v>
+        <v>4045.946393782434</v>
       </c>
       <c r="D55">
-        <v>6821.209870144145</v>
+        <v>6853.574393782435</v>
       </c>
       <c r="E55">
-        <v>2631.746</v>
+        <v>2687.928</v>
       </c>
       <c r="F55">
-        <v>2977.646</v>
+        <v>3033.828</v>
       </c>
       <c r="G55">
         <v>226.2</v>
@@ -5803,28 +5803,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M55">
-        <v>164.6638238</v>
+        <v>167.7706884</v>
       </c>
       <c r="N55">
-        <v>407.5443394653062</v>
+        <v>404.4374748653062</v>
       </c>
       <c r="O55">
-        <v>122.2633018395918</v>
+        <v>121.3312424595918</v>
       </c>
       <c r="P55">
-        <v>285.2810376257143</v>
+        <v>283.1062324057143</v>
       </c>
       <c r="Q55">
-        <v>888.4810376257144</v>
+        <v>886.3062324057144</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2090810252749219</v>
+        <v>0.2120354976342366</v>
       </c>
       <c r="T55">
-        <v>1.138467569025773</v>
+        <v>1.159067457830975</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.47500835374932</v>
+        <v>3.410656347198407</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1184397289117488</v>
+        <v>0.1180950759442843</v>
       </c>
       <c r="C56">
-        <v>4045.946393782434</v>
+        <v>4022.437500791493</v>
       </c>
       <c r="D56">
-        <v>6853.574393782435</v>
+        <v>6886.247500791494</v>
       </c>
       <c r="E56">
-        <v>2687.928</v>
+        <v>2744.11</v>
       </c>
       <c r="F56">
-        <v>3033.828</v>
+        <v>3090.01</v>
       </c>
       <c r="G56">
         <v>226.2</v>
@@ -5885,28 +5885,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M56">
-        <v>167.7706884</v>
+        <v>170.877553</v>
       </c>
       <c r="N56">
-        <v>404.4374748653062</v>
+        <v>401.3306102653062</v>
       </c>
       <c r="O56">
-        <v>121.3312424595918</v>
+        <v>120.3991830795919</v>
       </c>
       <c r="P56">
-        <v>283.1062324057143</v>
+        <v>280.9314271857143</v>
       </c>
       <c r="Q56">
-        <v>886.3062324057144</v>
+        <v>884.1314271857143</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2120354976342366</v>
+        <v>0.2151212798761874</v>
       </c>
       <c r="T56">
-        <v>1.159067457830975</v>
+        <v>1.180582897249742</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.410656347198407</v>
+        <v>3.348644413612981</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1180950759442843</v>
+        <v>0.1177504229768198</v>
       </c>
       <c r="C57">
-        <v>4022.437500791493</v>
+        <v>3999.241625648709</v>
       </c>
       <c r="D57">
-        <v>6886.247500791494</v>
+        <v>6919.233625648709</v>
       </c>
       <c r="E57">
-        <v>2744.11</v>
+        <v>2800.292</v>
       </c>
       <c r="F57">
-        <v>3090.01</v>
+        <v>3146.192</v>
       </c>
       <c r="G57">
         <v>226.2</v>
@@ -5967,28 +5967,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M57">
-        <v>170.877553</v>
+        <v>173.9844176</v>
       </c>
       <c r="N57">
-        <v>401.3306102653062</v>
+        <v>398.2237456653062</v>
       </c>
       <c r="O57">
-        <v>120.3991830795919</v>
+        <v>119.4671236995919</v>
       </c>
       <c r="P57">
-        <v>280.9314271857143</v>
+        <v>278.7566219657143</v>
       </c>
       <c r="Q57">
-        <v>884.1314271857143</v>
+        <v>881.9566219657144</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2151212798761874</v>
+        <v>0.2183473249473178</v>
       </c>
       <c r="T57">
-        <v>1.180582897249742</v>
+        <v>1.203076311187543</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.348644413612981</v>
+        <v>3.288847191941321</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1177504229768198</v>
+        <v>0.1174057700093553</v>
       </c>
       <c r="C58">
-        <v>3999.241625648709</v>
+        <v>3976.363288207583</v>
       </c>
       <c r="D58">
-        <v>6919.233625648709</v>
+        <v>6952.537288207584</v>
       </c>
       <c r="E58">
-        <v>2800.292</v>
+        <v>2856.474</v>
       </c>
       <c r="F58">
-        <v>3146.192</v>
+        <v>3202.374</v>
       </c>
       <c r="G58">
         <v>226.2</v>
@@ -6049,28 +6049,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M58">
-        <v>173.9844176</v>
+        <v>177.0912822</v>
       </c>
       <c r="N58">
-        <v>398.2237456653062</v>
+        <v>395.1168810653062</v>
       </c>
       <c r="O58">
-        <v>119.4671236995919</v>
+        <v>118.5350643195919</v>
       </c>
       <c r="P58">
-        <v>278.7566219657143</v>
+        <v>276.5818167457143</v>
       </c>
       <c r="Q58">
-        <v>881.9566219657144</v>
+        <v>879.7818167457144</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2183473249473178</v>
+        <v>0.2217234186264078</v>
       </c>
       <c r="T58">
-        <v>1.203076311187543</v>
+        <v>1.226615930424777</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.288847191941321</v>
+        <v>3.231148118398491</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1174057700093553</v>
+        <v>0.1170611170418908</v>
       </c>
       <c r="C59">
-        <v>3976.363288207583</v>
+        <v>3953.807095762349</v>
       </c>
       <c r="D59">
-        <v>6952.537288207584</v>
+        <v>6986.16309576235</v>
       </c>
       <c r="E59">
-        <v>2856.474</v>
+        <v>2912.656</v>
       </c>
       <c r="F59">
-        <v>3202.374</v>
+        <v>3258.556</v>
       </c>
       <c r="G59">
         <v>226.2</v>
@@ -6131,28 +6131,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M59">
-        <v>177.0912822</v>
+        <v>180.1981468</v>
       </c>
       <c r="N59">
-        <v>395.1168810653062</v>
+        <v>392.0100164653062</v>
       </c>
       <c r="O59">
-        <v>118.5350643195919</v>
+        <v>117.6030049395919</v>
       </c>
       <c r="P59">
-        <v>276.5818167457143</v>
+        <v>274.4070115257143</v>
       </c>
       <c r="Q59">
-        <v>879.7818167457144</v>
+        <v>877.6070115257144</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2217234186264078</v>
+        <v>0.2252602786711687</v>
       </c>
       <c r="T59">
-        <v>1.226615930424777</v>
+        <v>1.251276483911403</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.231148118398491</v>
+        <v>3.175438668081275</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1170611170418908</v>
+        <v>0.1167164640744263</v>
       </c>
       <c r="C60">
-        <v>3953.80709576235</v>
+        <v>3931.577745172768</v>
       </c>
       <c r="D60">
-        <v>6986.16309576235</v>
+        <v>7020.115745172768</v>
       </c>
       <c r="E60">
-        <v>2912.655999999999</v>
+        <v>2968.838</v>
       </c>
       <c r="F60">
-        <v>3258.556</v>
+        <v>3314.738</v>
       </c>
       <c r="G60">
         <v>226.2</v>
@@ -6213,28 +6213,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M60">
-        <v>180.1981468</v>
+        <v>183.3050114</v>
       </c>
       <c r="N60">
-        <v>392.0100164653062</v>
+        <v>388.9031518653062</v>
       </c>
       <c r="O60">
-        <v>117.6030049395919</v>
+        <v>116.6709455595919</v>
       </c>
       <c r="P60">
-        <v>274.4070115257143</v>
+        <v>272.2322063057143</v>
       </c>
       <c r="Q60">
-        <v>877.6070115257144</v>
+        <v>875.4322063057143</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2252602786711687</v>
+        <v>0.2289696684742106</v>
       </c>
       <c r="T60">
-        <v>1.251276483911403</v>
+        <v>1.277139991226645</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.175438668081276</v>
+        <v>3.121617673707017</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1167164640744263</v>
+        <v>0.1163718111069619</v>
       </c>
       <c r="C61">
-        <v>3931.577745172768</v>
+        <v>3909.680025051186</v>
       </c>
       <c r="D61">
-        <v>7020.115745172768</v>
+        <v>7054.400025051185</v>
       </c>
       <c r="E61">
-        <v>2968.838</v>
+        <v>3025.02</v>
       </c>
       <c r="F61">
-        <v>3314.738</v>
+        <v>3370.92</v>
       </c>
       <c r="G61">
         <v>226.2</v>
@@ -6295,28 +6295,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M61">
-        <v>183.3050114</v>
+        <v>186.411876</v>
       </c>
       <c r="N61">
-        <v>388.9031518653062</v>
+        <v>385.7962872653062</v>
       </c>
       <c r="O61">
-        <v>116.6709455595919</v>
+        <v>115.7388861795919</v>
       </c>
       <c r="P61">
-        <v>272.2322063057143</v>
+        <v>270.0574010857143</v>
       </c>
       <c r="Q61">
-        <v>875.4322063057143</v>
+        <v>873.2574010857144</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2289696684742106</v>
+        <v>0.2328645277674047</v>
       </c>
       <c r="T61">
-        <v>1.277139991226645</v>
+        <v>1.304296673907649</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.121617673707017</v>
+        <v>3.069590712478567</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1163718111069619</v>
+        <v>0.1160271581394974</v>
       </c>
       <c r="C62">
-        <v>3909.680025051186</v>
+        <v>3888.118818014016</v>
       </c>
       <c r="D62">
-        <v>7054.400025051185</v>
+        <v>7089.020818014016</v>
       </c>
       <c r="E62">
-        <v>3025.02</v>
+        <v>3081.202</v>
       </c>
       <c r="F62">
-        <v>3370.92</v>
+        <v>3427.102</v>
       </c>
       <c r="G62">
         <v>226.2</v>
@@ -6377,28 +6377,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M62">
-        <v>186.411876</v>
+        <v>189.5187406</v>
       </c>
       <c r="N62">
-        <v>385.7962872653062</v>
+        <v>382.6894226653062</v>
       </c>
       <c r="O62">
-        <v>115.7388861795919</v>
+        <v>114.8068267995919</v>
       </c>
       <c r="P62">
-        <v>270.0574010857143</v>
+        <v>267.8825958657143</v>
       </c>
       <c r="Q62">
-        <v>873.2574010857144</v>
+        <v>871.0825958657144</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2328645277674047</v>
+        <v>0.2369591234346086</v>
       </c>
       <c r="T62">
-        <v>1.304296673907649</v>
+        <v>1.33284600698255</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.069590712478567</v>
+        <v>3.019269553257606</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1160271581394974</v>
+        <v>0.1167675051720329</v>
       </c>
       <c r="C63">
-        <v>3888.118818014016</v>
+        <v>3757.982752509296</v>
       </c>
       <c r="D63">
-        <v>7089.020818014016</v>
+        <v>7015.066752509296</v>
       </c>
       <c r="E63">
-        <v>3081.202</v>
+        <v>3137.384</v>
       </c>
       <c r="F63">
-        <v>3427.102</v>
+        <v>3483.284</v>
       </c>
       <c r="G63">
         <v>226.2</v>
@@ -6459,45 +6459,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M63">
-        <v>189.5187406</v>
+        <v>201.3338152</v>
       </c>
       <c r="N63">
-        <v>382.6894226653062</v>
+        <v>370.8743480653062</v>
       </c>
       <c r="O63">
-        <v>114.8068267995919</v>
+        <v>111.2623044195919</v>
       </c>
       <c r="P63">
-        <v>267.8825958657143</v>
+        <v>259.6120436457144</v>
       </c>
       <c r="Q63">
-        <v>871.0825958657144</v>
+        <v>862.8120436457144</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2369591234346086</v>
+        <v>0.2412692241369286</v>
       </c>
       <c r="T63">
-        <v>1.33284600698255</v>
+        <v>1.362897936535078</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.019269553257606</v>
+        <v>2.842086723965812</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1167675051720329</v>
+        <v>0.1164403522045684</v>
       </c>
       <c r="C64">
-        <v>3757.982752509296</v>
+        <v>3734.289264152026</v>
       </c>
       <c r="D64">
-        <v>7015.066752509296</v>
+        <v>7047.555264152026</v>
       </c>
       <c r="E64">
-        <v>3137.384</v>
+        <v>3193.566</v>
       </c>
       <c r="F64">
-        <v>3483.284</v>
+        <v>3539.466</v>
       </c>
       <c r="G64">
         <v>226.2</v>
@@ -6541,28 +6541,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M64">
-        <v>201.3338152</v>
+        <v>204.5811348</v>
       </c>
       <c r="N64">
-        <v>370.8743480653062</v>
+        <v>367.6270284653062</v>
       </c>
       <c r="O64">
-        <v>111.2623044195919</v>
+        <v>110.2881085395919</v>
       </c>
       <c r="P64">
-        <v>259.6120436457144</v>
+        <v>257.3389199257144</v>
       </c>
       <c r="Q64">
-        <v>862.8120436457144</v>
+        <v>860.5389199257145</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2412692241369286</v>
+        <v>0.2458123032555903</v>
       </c>
       <c r="T64">
-        <v>1.362897936535078</v>
+        <v>1.394574294712068</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.842086723965812</v>
+        <v>2.796974236283815</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1164403522045684</v>
+        <v>0.1161131992371039</v>
       </c>
       <c r="C65">
-        <v>3734.289264152026</v>
+        <v>3710.898100624461</v>
       </c>
       <c r="D65">
-        <v>7047.555264152026</v>
+        <v>7080.346100624462</v>
       </c>
       <c r="E65">
-        <v>3193.566</v>
+        <v>3249.748</v>
       </c>
       <c r="F65">
-        <v>3539.466</v>
+        <v>3595.648</v>
       </c>
       <c r="G65">
         <v>226.2</v>
@@ -6623,28 +6623,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M65">
-        <v>204.5811348</v>
+        <v>207.8284544</v>
       </c>
       <c r="N65">
-        <v>367.6270284653062</v>
+        <v>364.3797088653062</v>
       </c>
       <c r="O65">
-        <v>110.2881085395919</v>
+        <v>109.3139126595918</v>
       </c>
       <c r="P65">
-        <v>257.3389199257144</v>
+        <v>255.0657962057143</v>
       </c>
       <c r="Q65">
-        <v>860.5389199257145</v>
+        <v>858.2657962057144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2458123032555903</v>
+        <v>0.2506077756586219</v>
       </c>
       <c r="T65">
-        <v>1.394574294712068</v>
+        <v>1.428010450565556</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.796974236283815</v>
+        <v>2.75327151384188</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1161131992371039</v>
+        <v>0.1157860462696394</v>
       </c>
       <c r="C66">
-        <v>3710.898100624461</v>
+        <v>3687.813501620233</v>
       </c>
       <c r="D66">
-        <v>7080.346100624462</v>
+        <v>7113.443501620233</v>
       </c>
       <c r="E66">
-        <v>3249.748</v>
+        <v>3305.93</v>
       </c>
       <c r="F66">
-        <v>3595.648</v>
+        <v>3651.83</v>
       </c>
       <c r="G66">
         <v>226.2</v>
@@ -6705,28 +6705,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M66">
-        <v>207.8284544</v>
+        <v>211.075774</v>
       </c>
       <c r="N66">
-        <v>364.3797088653062</v>
+        <v>361.1323892653062</v>
       </c>
       <c r="O66">
-        <v>109.3139126595918</v>
+        <v>108.3397167795919</v>
       </c>
       <c r="P66">
-        <v>255.0657962057143</v>
+        <v>252.7926724857143</v>
       </c>
       <c r="Q66">
-        <v>858.2657962057144</v>
+        <v>855.9926724857144</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2506077756586219</v>
+        <v>0.2556772750561125</v>
       </c>
       <c r="T66">
-        <v>1.428010450565556</v>
+        <v>1.463357243896386</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.75327151384188</v>
+        <v>2.710913490552005</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1157860462696394</v>
+        <v>0.1154588933021749</v>
       </c>
       <c r="C67">
-        <v>3687.813501620233</v>
+        <v>3665.039786479871</v>
       </c>
       <c r="D67">
-        <v>7113.443501620233</v>
+        <v>7146.851786479871</v>
       </c>
       <c r="E67">
-        <v>3305.93</v>
+        <v>3362.112</v>
       </c>
       <c r="F67">
-        <v>3651.83</v>
+        <v>3708.012</v>
       </c>
       <c r="G67">
         <v>226.2</v>
@@ -6787,28 +6787,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M67">
-        <v>211.075774</v>
+        <v>214.3230936</v>
       </c>
       <c r="N67">
-        <v>361.1323892653062</v>
+        <v>357.8850696653062</v>
       </c>
       <c r="O67">
-        <v>108.3397167795919</v>
+        <v>107.3655208995919</v>
       </c>
       <c r="P67">
-        <v>252.7926724857143</v>
+        <v>250.5195487657144</v>
       </c>
       <c r="Q67">
-        <v>855.9926724857144</v>
+        <v>853.7195487657144</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2556772750561125</v>
+        <v>0.2610449803005144</v>
       </c>
       <c r="T67">
-        <v>1.463357243896386</v>
+        <v>1.500783260364325</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.710913490552005</v>
+        <v>2.669839043725459</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1154588933021749</v>
+        <v>0.1151317403347104</v>
       </c>
       <c r="C68">
-        <v>3665.039786479871</v>
+        <v>3642.581356069905</v>
       </c>
       <c r="D68">
-        <v>7146.851786479871</v>
+        <v>7180.575356069905</v>
       </c>
       <c r="E68">
-        <v>3362.112</v>
+        <v>3418.294</v>
       </c>
       <c r="F68">
-        <v>3708.012</v>
+        <v>3764.194</v>
       </c>
       <c r="G68">
         <v>226.2</v>
@@ -6869,28 +6869,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M68">
-        <v>214.3230936</v>
+        <v>217.5704132</v>
       </c>
       <c r="N68">
-        <v>357.8850696653062</v>
+        <v>354.6377500653062</v>
       </c>
       <c r="O68">
-        <v>107.3655208995919</v>
+        <v>106.3913250195919</v>
       </c>
       <c r="P68">
-        <v>250.5195487657144</v>
+        <v>248.2464250457143</v>
       </c>
       <c r="Q68">
-        <v>853.7195487657144</v>
+        <v>851.4464250457144</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2610449803005144</v>
+        <v>0.266738001014274</v>
       </c>
       <c r="T68">
-        <v>1.500783260364325</v>
+        <v>1.540477520254562</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.669839043725459</v>
+        <v>2.629990699789259</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1151317403347104</v>
+        <v>0.1148045873672459</v>
       </c>
       <c r="C69">
-        <v>3642.581356069905</v>
+        <v>3620.44269471547</v>
       </c>
       <c r="D69">
-        <v>7180.575356069905</v>
+        <v>7214.61869471547</v>
       </c>
       <c r="E69">
-        <v>3418.294</v>
+        <v>3474.476</v>
       </c>
       <c r="F69">
-        <v>3764.194</v>
+        <v>3820.376</v>
       </c>
       <c r="G69">
         <v>226.2</v>
@@ -6951,28 +6951,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M69">
-        <v>217.5704132</v>
+        <v>220.8177328</v>
       </c>
       <c r="N69">
-        <v>354.6377500653062</v>
+        <v>351.3904304653062</v>
       </c>
       <c r="O69">
-        <v>106.3913250195919</v>
+        <v>105.4171291395919</v>
       </c>
       <c r="P69">
-        <v>248.2464250457143</v>
+        <v>245.9733013257143</v>
       </c>
       <c r="Q69">
-        <v>851.4464250457144</v>
+        <v>849.1733013257144</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.266738001014274</v>
+        <v>0.2727868355226435</v>
       </c>
       <c r="T69">
-        <v>1.540477520254562</v>
+        <v>1.58265267138794</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.629990699789259</v>
+        <v>2.591314365968828</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1148045873672459</v>
+        <v>0.1144774343997814</v>
       </c>
       <c r="C70">
-        <v>3620.44269471547</v>
+        <v>3598.628372188123</v>
       </c>
       <c r="D70">
-        <v>7214.61869471547</v>
+        <v>7248.986372188123</v>
       </c>
       <c r="E70">
-        <v>3474.476</v>
+        <v>3530.658</v>
       </c>
       <c r="F70">
-        <v>3820.376</v>
+        <v>3876.558</v>
       </c>
       <c r="G70">
         <v>226.2</v>
@@ -7033,28 +7033,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M70">
-        <v>220.8177328</v>
+        <v>224.0650524</v>
       </c>
       <c r="N70">
-        <v>351.3904304653062</v>
+        <v>348.1431108653062</v>
       </c>
       <c r="O70">
-        <v>105.4171291395919</v>
+        <v>104.4429332595919</v>
       </c>
       <c r="P70">
-        <v>245.9733013257143</v>
+        <v>243.7001776057143</v>
       </c>
       <c r="Q70">
-        <v>849.1733013257144</v>
+        <v>846.9001776057144</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2727868355226435</v>
+        <v>0.2792259174186498</v>
       </c>
       <c r="T70">
-        <v>1.58265267138794</v>
+        <v>1.627548800013793</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.591314365968828</v>
+        <v>2.553759085302613</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1144774343997814</v>
+        <v>0.1141502814323169</v>
       </c>
       <c r="C71">
-        <v>3598.628372188123</v>
+        <v>3577.143045750754</v>
       </c>
       <c r="D71">
-        <v>7248.986372188123</v>
+        <v>7283.683045750755</v>
       </c>
       <c r="E71">
-        <v>3530.658</v>
+        <v>3586.84</v>
       </c>
       <c r="F71">
-        <v>3876.558</v>
+        <v>3932.74</v>
       </c>
       <c r="G71">
         <v>226.2</v>
@@ -7115,28 +7115,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M71">
-        <v>224.0650524</v>
+        <v>227.312372</v>
       </c>
       <c r="N71">
-        <v>348.1431108653062</v>
+        <v>344.8957912653062</v>
       </c>
       <c r="O71">
-        <v>104.4429332595919</v>
+        <v>103.4687373795918</v>
       </c>
       <c r="P71">
-        <v>243.7001776057143</v>
+        <v>241.4270538857143</v>
       </c>
       <c r="Q71">
-        <v>846.9001776057144</v>
+        <v>844.6270538857143</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2792259174186498</v>
+        <v>0.2860942714410564</v>
       </c>
       <c r="T71">
-        <v>1.627548800013793</v>
+        <v>1.67543800388137</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.553759085302613</v>
+        <v>2.517276812655433</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1141502814323169</v>
+        <v>0.1155626284648524</v>
       </c>
       <c r="C72">
-        <v>3577.143045750754</v>
+        <v>3373.502609020864</v>
       </c>
       <c r="D72">
-        <v>7283.683045750755</v>
+        <v>7136.224609020865</v>
       </c>
       <c r="E72">
-        <v>3586.84</v>
+        <v>3643.022</v>
       </c>
       <c r="F72">
-        <v>3932.74</v>
+        <v>3988.922</v>
       </c>
       <c r="G72">
         <v>226.2</v>
@@ -7197,45 +7197,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M72">
-        <v>227.312372</v>
+        <v>244.5209186</v>
       </c>
       <c r="N72">
-        <v>344.8957912653062</v>
+        <v>327.6872446653061</v>
       </c>
       <c r="O72">
-        <v>103.4687373795918</v>
+        <v>98.30617339959184</v>
       </c>
       <c r="P72">
-        <v>241.4270538857143</v>
+        <v>229.3810712657143</v>
       </c>
       <c r="Q72">
-        <v>844.6270538857143</v>
+        <v>832.5810712657144</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2860942714410564</v>
+        <v>0.2934363050512153</v>
       </c>
       <c r="T72">
-        <v>1.67543800388137</v>
+        <v>1.726629911463953</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.3</v>
       </c>
       <c r="W72">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.517276812655433</v>
+        <v>2.340119473382782</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1155626284648524</v>
+        <v>0.1152599754973879</v>
       </c>
       <c r="C73">
-        <v>3373.502609020865</v>
+        <v>3348.414768483885</v>
       </c>
       <c r="D73">
-        <v>7136.224609020865</v>
+        <v>7167.318768483885</v>
       </c>
       <c r="E73">
-        <v>3643.021999999999</v>
+        <v>3699.204</v>
       </c>
       <c r="F73">
-        <v>3988.922</v>
+        <v>4045.104</v>
       </c>
       <c r="G73">
         <v>226.2</v>
@@ -7279,28 +7279,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M73">
-        <v>244.5209186</v>
+        <v>247.9648752</v>
       </c>
       <c r="N73">
-        <v>327.6872446653063</v>
+        <v>324.2432880653062</v>
       </c>
       <c r="O73">
-        <v>98.30617339959187</v>
+        <v>97.27298641959186</v>
       </c>
       <c r="P73">
-        <v>229.3810712657144</v>
+        <v>226.9703016457144</v>
       </c>
       <c r="Q73">
-        <v>832.5810712657144</v>
+        <v>830.1703016457144</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2934363050512152</v>
+        <v>0.3013027696335283</v>
       </c>
       <c r="T73">
-        <v>1.726629911463952</v>
+        <v>1.781478383873862</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.340119473382782</v>
+        <v>2.307617814030244</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1152599754973879</v>
+        <v>0.1149573225299234</v>
       </c>
       <c r="C74">
-        <v>3348.414768483885</v>
+        <v>3323.599082486383</v>
       </c>
       <c r="D74">
-        <v>7167.318768483885</v>
+        <v>7198.685082486383</v>
       </c>
       <c r="E74">
-        <v>3699.204</v>
+        <v>3755.386</v>
       </c>
       <c r="F74">
-        <v>4045.104</v>
+        <v>4101.286</v>
       </c>
       <c r="G74">
         <v>226.2</v>
@@ -7361,28 +7361,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M74">
-        <v>247.9648752</v>
+        <v>251.4088318</v>
       </c>
       <c r="N74">
-        <v>324.2432880653062</v>
+        <v>320.7993314653062</v>
       </c>
       <c r="O74">
-        <v>97.27298641959186</v>
+        <v>96.23979943959185</v>
       </c>
       <c r="P74">
-        <v>226.9703016457144</v>
+        <v>224.5595320257143</v>
       </c>
       <c r="Q74">
-        <v>830.1703016457144</v>
+        <v>827.7595320257144</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3013027696335283</v>
+        <v>0.3097519352960127</v>
       </c>
       <c r="T74">
-        <v>1.781478383873862</v>
+        <v>1.840389706091913</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.307617814030244</v>
+        <v>2.276006611098323</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1149573225299234</v>
+        <v>0.1161050695624589</v>
       </c>
       <c r="C75">
-        <v>3323.599082486383</v>
+        <v>3149.8968312015</v>
       </c>
       <c r="D75">
-        <v>7198.685082486383</v>
+        <v>7081.1648312015</v>
       </c>
       <c r="E75">
-        <v>3755.386</v>
+        <v>3811.568</v>
       </c>
       <c r="F75">
-        <v>4101.286</v>
+        <v>4157.468</v>
       </c>
       <c r="G75">
         <v>226.2</v>
@@ -7443,45 +7443,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M75">
-        <v>251.4088318</v>
+        <v>266.4936988</v>
       </c>
       <c r="N75">
-        <v>320.7993314653062</v>
+        <v>305.7144644653062</v>
       </c>
       <c r="O75">
-        <v>96.23979943959185</v>
+        <v>91.71433933959186</v>
       </c>
       <c r="P75">
-        <v>224.5595320257143</v>
+        <v>214.0001251257144</v>
       </c>
       <c r="Q75">
-        <v>827.7595320257144</v>
+        <v>817.2001251257144</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3097519352960127</v>
+        <v>0.3188510367786882</v>
       </c>
       <c r="T75">
-        <v>1.840389706091913</v>
+        <v>1.903832668480583</v>
       </c>
       <c r="U75">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V75">
         <v>0.3</v>
       </c>
       <c r="W75">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.276006611098323</v>
+        <v>2.147173332209783</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1161050695624589</v>
+        <v>0.1158220165949944</v>
       </c>
       <c r="C76">
-        <v>3149.8968312015</v>
+        <v>3122.339324125918</v>
       </c>
       <c r="D76">
-        <v>7081.1648312015</v>
+        <v>7109.789324125918</v>
       </c>
       <c r="E76">
-        <v>3811.568</v>
+        <v>3867.75</v>
       </c>
       <c r="F76">
-        <v>4157.468</v>
+        <v>4213.65</v>
       </c>
       <c r="G76">
         <v>226.2</v>
@@ -7525,28 +7525,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M76">
-        <v>266.4936988</v>
+        <v>270.094965</v>
       </c>
       <c r="N76">
-        <v>305.7144644653062</v>
+        <v>302.1131982653062</v>
       </c>
       <c r="O76">
-        <v>91.71433933959186</v>
+        <v>90.63395947959187</v>
       </c>
       <c r="P76">
-        <v>214.0001251257144</v>
+        <v>211.4792387857144</v>
       </c>
       <c r="Q76">
-        <v>817.2001251257144</v>
+        <v>814.6792387857145</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3188510367786882</v>
+        <v>0.3286780663799778</v>
       </c>
       <c r="T76">
-        <v>1.903832668480583</v>
+        <v>1.972351067860347</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.147173332209783</v>
+        <v>2.118544354446986</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1158220165949944</v>
+        <v>0.11553896362753</v>
       </c>
       <c r="C77">
-        <v>3122.339324125918</v>
+        <v>3095.01417632965</v>
       </c>
       <c r="D77">
-        <v>7109.789324125918</v>
+        <v>7138.64617632965</v>
       </c>
       <c r="E77">
-        <v>3867.75</v>
+        <v>3923.932</v>
       </c>
       <c r="F77">
-        <v>4213.65</v>
+        <v>4269.832</v>
       </c>
       <c r="G77">
         <v>226.2</v>
@@ -7607,28 +7607,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M77">
-        <v>270.094965</v>
+        <v>273.6962312000001</v>
       </c>
       <c r="N77">
-        <v>302.1131982653062</v>
+        <v>298.5119320653062</v>
       </c>
       <c r="O77">
-        <v>90.63395947959187</v>
+        <v>89.55357961959184</v>
       </c>
       <c r="P77">
-        <v>211.4792387857144</v>
+        <v>208.9583524457143</v>
       </c>
       <c r="Q77">
-        <v>814.6792387857145</v>
+        <v>812.1583524457144</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3286780663799778</v>
+        <v>0.3393240151147082</v>
       </c>
       <c r="T77">
-        <v>1.972351067860347</v>
+        <v>2.046579333855091</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.118544354446986</v>
+        <v>2.09066877083584</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.11553896362753</v>
+        <v>0.1152559106600655</v>
       </c>
       <c r="C78">
-        <v>3095.01417632965</v>
+        <v>3067.924228606937</v>
       </c>
       <c r="D78">
-        <v>7138.64617632965</v>
+        <v>7167.738228606937</v>
       </c>
       <c r="E78">
-        <v>3923.932</v>
+        <v>3980.114</v>
       </c>
       <c r="F78">
-        <v>4269.832</v>
+        <v>4326.014</v>
       </c>
       <c r="G78">
         <v>226.2</v>
@@ -7689,28 +7689,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M78">
-        <v>273.6962312000001</v>
+        <v>277.2974974000001</v>
       </c>
       <c r="N78">
-        <v>298.5119320653062</v>
+        <v>294.9106658653062</v>
       </c>
       <c r="O78">
-        <v>89.55357961959184</v>
+        <v>88.47319975959185</v>
       </c>
       <c r="P78">
-        <v>208.9583524457143</v>
+        <v>206.4374661057143</v>
       </c>
       <c r="Q78">
-        <v>812.1583524457144</v>
+        <v>809.6374661057143</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3393240151147082</v>
+        <v>0.3508956985220237</v>
       </c>
       <c r="T78">
-        <v>2.046579333855091</v>
+        <v>2.127262231675465</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.09066877083584</v>
+        <v>2.063517228357453</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1152559106600655</v>
+        <v>0.114972857692601</v>
       </c>
       <c r="C79">
-        <v>3067.924228606937</v>
+        <v>3041.072368249744</v>
       </c>
       <c r="D79">
-        <v>7167.738228606937</v>
+        <v>7197.068368249744</v>
       </c>
       <c r="E79">
-        <v>3980.114</v>
+        <v>4036.296</v>
       </c>
       <c r="F79">
-        <v>4326.014</v>
+        <v>4382.196</v>
       </c>
       <c r="G79">
         <v>226.2</v>
@@ -7771,28 +7771,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M79">
-        <v>277.2974974000001</v>
+        <v>280.8987636</v>
       </c>
       <c r="N79">
-        <v>294.9106658653062</v>
+        <v>291.3093996653062</v>
       </c>
       <c r="O79">
-        <v>88.47319975959185</v>
+        <v>87.39281989959186</v>
       </c>
       <c r="P79">
-        <v>206.4374661057143</v>
+        <v>203.9165797657143</v>
       </c>
       <c r="Q79">
-        <v>809.6374661057143</v>
+        <v>807.1165797657144</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3508956985220237</v>
+        <v>0.3635193531481862</v>
       </c>
       <c r="T79">
-        <v>2.127262231675465</v>
+        <v>2.215279938388601</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.063517228357453</v>
+        <v>2.037061879275948</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.114972857692601</v>
+        <v>0.1146898047251365</v>
       </c>
       <c r="C80">
-        <v>3041.072368249744</v>
+        <v>3014.461530003009</v>
       </c>
       <c r="D80">
-        <v>7197.068368249744</v>
+        <v>7226.639530003009</v>
       </c>
       <c r="E80">
-        <v>4036.296</v>
+        <v>4092.478</v>
       </c>
       <c r="F80">
-        <v>4382.196</v>
+        <v>4438.378</v>
       </c>
       <c r="G80">
         <v>226.2</v>
@@ -7853,28 +7853,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M80">
-        <v>280.8987636</v>
+        <v>284.5000298</v>
       </c>
       <c r="N80">
-        <v>291.3093996653062</v>
+        <v>287.7081334653062</v>
       </c>
       <c r="O80">
-        <v>87.39281989959186</v>
+        <v>86.31244003959186</v>
       </c>
       <c r="P80">
-        <v>203.9165797657143</v>
+        <v>201.3956934257143</v>
       </c>
       <c r="Q80">
-        <v>807.1165797657144</v>
+        <v>804.5956934257144</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3635193531481862</v>
+        <v>0.377345260595888</v>
       </c>
       <c r="T80">
-        <v>2.215279938388601</v>
+        <v>2.311680283836321</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.037061879275948</v>
+        <v>2.011276285867392</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1146898047251365</v>
+        <v>0.118774751757672</v>
       </c>
       <c r="C81">
-        <v>3014.461530003009</v>
+        <v>2553.750031892233</v>
       </c>
       <c r="D81">
-        <v>7226.639530003009</v>
+        <v>6822.110031892234</v>
       </c>
       <c r="E81">
-        <v>4092.478</v>
+        <v>4148.660000000001</v>
       </c>
       <c r="F81">
-        <v>4438.378</v>
+        <v>4494.56</v>
       </c>
       <c r="G81">
         <v>226.2</v>
@@ -7935,45 +7935,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M81">
-        <v>284.5000298</v>
+        <v>323.1588640000001</v>
       </c>
       <c r="N81">
-        <v>287.7081334653062</v>
+        <v>249.0492992653062</v>
       </c>
       <c r="O81">
-        <v>86.31244003959186</v>
+        <v>74.71478977959184</v>
       </c>
       <c r="P81">
-        <v>201.3956934257143</v>
+        <v>174.3345094857143</v>
       </c>
       <c r="Q81">
-        <v>804.5956934257144</v>
+        <v>777.5345094857144</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.377345260595888</v>
+        <v>0.3925537587883599</v>
       </c>
       <c r="T81">
-        <v>2.311680283836321</v>
+        <v>2.417720663828812</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.3</v>
       </c>
       <c r="W81">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.011276285867392</v>
+        <v>1.77067141585603</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.118774751757672</v>
+        <v>0.1207575987902075</v>
       </c>
       <c r="C82">
-        <v>2553.750031892233</v>
+        <v>2317.103331172185</v>
       </c>
       <c r="D82">
-        <v>6822.110031892234</v>
+        <v>6641.645331172185</v>
       </c>
       <c r="E82">
-        <v>4148.660000000001</v>
+        <v>4204.842000000001</v>
       </c>
       <c r="F82">
-        <v>4494.56</v>
+        <v>4550.742</v>
       </c>
       <c r="G82">
         <v>226.2</v>
@@ -8017,45 +8017,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M82">
-        <v>323.1588640000001</v>
+        <v>344.9462436000001</v>
       </c>
       <c r="N82">
-        <v>249.0492992653062</v>
+        <v>227.2619196653062</v>
       </c>
       <c r="O82">
-        <v>74.71478977959184</v>
+        <v>68.17857589959185</v>
       </c>
       <c r="P82">
-        <v>174.3345094857143</v>
+        <v>159.0833437657143</v>
       </c>
       <c r="Q82">
-        <v>777.5345094857144</v>
+        <v>762.2833437657143</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3925537587883599</v>
+        <v>0.4093631515274079</v>
       </c>
       <c r="T82">
-        <v>2.417720663828812</v>
+        <v>2.534923189083672</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.77067141585603</v>
+        <v>1.658832858399929</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1207575987902075</v>
+        <v>0.120556445822743</v>
       </c>
       <c r="C83">
-        <v>2317.103331172185</v>
+        <v>2278.792521442248</v>
       </c>
       <c r="D83">
-        <v>6641.645331172185</v>
+        <v>6659.516521442248</v>
       </c>
       <c r="E83">
-        <v>4204.842000000001</v>
+        <v>4261.024</v>
       </c>
       <c r="F83">
-        <v>4550.742</v>
+        <v>4606.924</v>
       </c>
       <c r="G83">
         <v>226.2</v>
@@ -8099,28 +8099,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M83">
-        <v>344.9462436000001</v>
+        <v>349.2048392</v>
       </c>
       <c r="N83">
-        <v>227.2619196653062</v>
+        <v>223.0033240653062</v>
       </c>
       <c r="O83">
-        <v>68.17857589959185</v>
+        <v>66.90099721959184</v>
       </c>
       <c r="P83">
-        <v>159.0833437657143</v>
+        <v>156.1023268457143</v>
       </c>
       <c r="Q83">
-        <v>762.2833437657143</v>
+        <v>759.3023268457143</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4093631515274079</v>
+        <v>0.4280402545707945</v>
       </c>
       <c r="T83">
-        <v>2.534923189083672</v>
+        <v>2.665148217144627</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.658832858399929</v>
+        <v>1.638603189395052</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.120556445822743</v>
+        <v>0.1203552928552785</v>
       </c>
       <c r="C84">
-        <v>2278.792521442248</v>
+        <v>2240.578145991283</v>
       </c>
       <c r="D84">
-        <v>6659.516521442248</v>
+        <v>6677.484145991284</v>
       </c>
       <c r="E84">
-        <v>4261.024</v>
+        <v>4317.206000000001</v>
       </c>
       <c r="F84">
-        <v>4606.924</v>
+        <v>4663.106000000001</v>
       </c>
       <c r="G84">
         <v>226.2</v>
@@ -8181,28 +8181,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M84">
-        <v>349.2048392</v>
+        <v>353.4634348000001</v>
       </c>
       <c r="N84">
-        <v>223.0033240653062</v>
+        <v>218.7447284653061</v>
       </c>
       <c r="O84">
-        <v>66.90099721959184</v>
+        <v>65.62341853959184</v>
       </c>
       <c r="P84">
-        <v>156.1023268457143</v>
+        <v>153.1213099257143</v>
       </c>
       <c r="Q84">
-        <v>759.3023268457143</v>
+        <v>756.3213099257143</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4280402545707945</v>
+        <v>0.4489146638545795</v>
       </c>
       <c r="T84">
-        <v>2.665148217144627</v>
+        <v>2.810693836742165</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.638603189395052</v>
+        <v>1.618860982293906</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1203552928552785</v>
+        <v>0.120154139887814</v>
       </c>
       <c r="C85">
-        <v>2240.578145991283</v>
+        <v>2202.460987480807</v>
       </c>
       <c r="D85">
-        <v>6677.484145991284</v>
+        <v>6695.548987480807</v>
       </c>
       <c r="E85">
-        <v>4317.206000000001</v>
+        <v>4373.388000000001</v>
       </c>
       <c r="F85">
-        <v>4663.106000000001</v>
+        <v>4719.288</v>
       </c>
       <c r="G85">
         <v>226.2</v>
@@ -8263,28 +8263,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M85">
-        <v>353.4634348000001</v>
+        <v>357.7220304000001</v>
       </c>
       <c r="N85">
-        <v>218.7447284653061</v>
+        <v>214.4861328653062</v>
       </c>
       <c r="O85">
-        <v>65.62341853959184</v>
+        <v>64.34583985959185</v>
       </c>
       <c r="P85">
-        <v>153.1213099257143</v>
+        <v>150.1402930057143</v>
       </c>
       <c r="Q85">
-        <v>756.3213099257143</v>
+        <v>753.3402930057143</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4489146638545795</v>
+        <v>0.4723983742988377</v>
       </c>
       <c r="T85">
-        <v>2.810693836742165</v>
+        <v>2.974432658789396</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.618860982293906</v>
+        <v>1.599588827742788</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.120154139887814</v>
+        <v>0.1199529869203495</v>
       </c>
       <c r="C86">
-        <v>2202.460987480809</v>
+        <v>2164.441837064767</v>
       </c>
       <c r="D86">
-        <v>6695.548987480809</v>
+        <v>6713.711837064767</v>
       </c>
       <c r="E86">
-        <v>4373.388</v>
+        <v>4429.57</v>
       </c>
       <c r="F86">
-        <v>4719.288</v>
+        <v>4775.469999999999</v>
       </c>
       <c r="G86">
         <v>226.2</v>
@@ -8345,28 +8345,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M86">
-        <v>357.7220304</v>
+        <v>361.980626</v>
       </c>
       <c r="N86">
-        <v>214.4861328653062</v>
+        <v>210.2275372653062</v>
       </c>
       <c r="O86">
-        <v>64.34583985959186</v>
+        <v>63.06826117959187</v>
       </c>
       <c r="P86">
-        <v>150.1402930057143</v>
+        <v>147.1592760857144</v>
       </c>
       <c r="Q86">
-        <v>753.3402930057143</v>
+        <v>750.3592760857144</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4723983742988374</v>
+        <v>0.4990132461356633</v>
       </c>
       <c r="T86">
-        <v>2.974432658789393</v>
+        <v>3.160003323776254</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.599588827742789</v>
+        <v>1.580770135651697</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1199529869203495</v>
+        <v>0.119751833952885</v>
       </c>
       <c r="C87">
-        <v>2164.441837064767</v>
+        <v>2126.521494505035</v>
       </c>
       <c r="D87">
-        <v>6713.711837064767</v>
+        <v>6731.973494505035</v>
       </c>
       <c r="E87">
-        <v>4429.57</v>
+        <v>4485.752</v>
       </c>
       <c r="F87">
-        <v>4775.469999999999</v>
+        <v>4831.652</v>
       </c>
       <c r="G87">
         <v>226.2</v>
@@ -8427,28 +8427,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M87">
-        <v>361.980626</v>
+        <v>366.2392216</v>
       </c>
       <c r="N87">
-        <v>210.2275372653062</v>
+        <v>205.9689416653062</v>
       </c>
       <c r="O87">
-        <v>63.06826117959187</v>
+        <v>61.79068249959186</v>
       </c>
       <c r="P87">
-        <v>147.1592760857144</v>
+        <v>144.1782591657143</v>
       </c>
       <c r="Q87">
-        <v>750.3592760857144</v>
+        <v>747.3782591657143</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4990132461356633</v>
+        <v>0.529430242520607</v>
       </c>
       <c r="T87">
-        <v>3.160003323776254</v>
+        <v>3.372084083761238</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.580770135651697</v>
+        <v>1.562389087562724</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.119751833952885</v>
+        <v>0.1195506809854205</v>
       </c>
       <c r="C88">
-        <v>2126.521494505035</v>
+        <v>2088.700768288794</v>
       </c>
       <c r="D88">
-        <v>6731.973494505035</v>
+        <v>6750.334768288794</v>
       </c>
       <c r="E88">
-        <v>4485.752</v>
+        <v>4541.934</v>
       </c>
       <c r="F88">
-        <v>4831.652</v>
+        <v>4887.834</v>
       </c>
       <c r="G88">
         <v>226.2</v>
@@ -8509,28 +8509,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M88">
-        <v>366.2392216</v>
+        <v>370.4978172</v>
       </c>
       <c r="N88">
-        <v>205.9689416653062</v>
+        <v>201.7103460653062</v>
       </c>
       <c r="O88">
-        <v>61.79068249959186</v>
+        <v>60.51310381959185</v>
       </c>
       <c r="P88">
-        <v>144.1782591657143</v>
+        <v>141.1972422457143</v>
       </c>
       <c r="Q88">
-        <v>747.3782591657143</v>
+        <v>744.3972422457143</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.529430242520607</v>
+        <v>0.5645267768109269</v>
       </c>
       <c r="T88">
-        <v>3.372084083761238</v>
+        <v>3.61679265297468</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.562389087562724</v>
+        <v>1.544430592303382</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1195506809854205</v>
+        <v>0.119349528017956</v>
       </c>
       <c r="C89">
-        <v>2088.700768288794</v>
+        <v>2050.980475747863</v>
       </c>
       <c r="D89">
-        <v>6750.334768288794</v>
+        <v>6768.796475747863</v>
       </c>
       <c r="E89">
-        <v>4541.934</v>
+        <v>4598.116</v>
       </c>
       <c r="F89">
-        <v>4887.834</v>
+        <v>4944.016</v>
       </c>
       <c r="G89">
         <v>226.2</v>
@@ -8591,28 +8591,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M89">
-        <v>370.4978172</v>
+        <v>374.7564128</v>
       </c>
       <c r="N89">
-        <v>201.7103460653062</v>
+        <v>197.4517504653062</v>
       </c>
       <c r="O89">
-        <v>60.51310381959185</v>
+        <v>59.23552513959186</v>
       </c>
       <c r="P89">
-        <v>141.1972422457143</v>
+        <v>138.2162253257143</v>
       </c>
       <c r="Q89">
-        <v>744.3972422457143</v>
+        <v>741.4162253257143</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5645267768109269</v>
+        <v>0.6054727334829668</v>
       </c>
       <c r="T89">
-        <v>3.61679265297468</v>
+        <v>3.902285983723698</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.544430592303382</v>
+        <v>1.526880244663571</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.119349528017956</v>
+        <v>0.1191483750504915</v>
       </c>
       <c r="C90">
-        <v>2050.980475747863</v>
+        <v>2013.361443179965</v>
       </c>
       <c r="D90">
-        <v>6768.796475747863</v>
+        <v>6787.359443179966</v>
       </c>
       <c r="E90">
-        <v>4598.116</v>
+        <v>4654.298000000001</v>
       </c>
       <c r="F90">
-        <v>4944.016</v>
+        <v>5000.198</v>
       </c>
       <c r="G90">
         <v>226.2</v>
@@ -8673,28 +8673,28 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M90">
-        <v>374.7564128</v>
+        <v>379.0150084000001</v>
       </c>
       <c r="N90">
-        <v>197.4517504653062</v>
+        <v>193.1931548653062</v>
       </c>
       <c r="O90">
-        <v>59.23552513959186</v>
+        <v>57.95794645959185</v>
       </c>
       <c r="P90">
-        <v>138.2162253257143</v>
+        <v>135.2352084057143</v>
       </c>
       <c r="Q90">
-        <v>741.4162253257143</v>
+        <v>738.4352084057143</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6054727334829668</v>
+        <v>0.6538634095499228</v>
       </c>
       <c r="T90">
-        <v>3.902285983723698</v>
+        <v>4.239687192790717</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.526880244663571</v>
+        <v>1.509724286858362</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1191483750504915</v>
+        <v>0.127893222083027</v>
       </c>
       <c r="C91">
-        <v>2013.361443179965</v>
+        <v>1234.167011953736</v>
       </c>
       <c r="D91">
-        <v>6787.359443179966</v>
+        <v>6064.347011953736</v>
       </c>
       <c r="E91">
-        <v>4654.298000000001</v>
+        <v>4710.48</v>
       </c>
       <c r="F91">
-        <v>5000.198</v>
+        <v>5056.38</v>
       </c>
       <c r="G91">
         <v>226.2</v>
@@ -8755,45 +8755,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M91">
-        <v>379.0150084000001</v>
+        <v>455.0742</v>
       </c>
       <c r="N91">
-        <v>193.1931548653062</v>
+        <v>117.1339632653062</v>
       </c>
       <c r="O91">
-        <v>57.95794645959185</v>
+        <v>35.14018897959185</v>
       </c>
       <c r="P91">
-        <v>135.2352084057143</v>
+        <v>81.99377428571434</v>
       </c>
       <c r="Q91">
-        <v>738.4352084057143</v>
+        <v>685.1937742857144</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6538634095499228</v>
+        <v>0.7119322208302702</v>
       </c>
       <c r="T91">
-        <v>4.239687192790717</v>
+        <v>4.64456864367114</v>
       </c>
       <c r="U91">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V91">
         <v>0.3</v>
       </c>
       <c r="W91">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.509724286858362</v>
+        <v>1.257395306667146</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.127893222083027</v>
+        <v>0.1492354540168496</v>
       </c>
       <c r="C92">
-        <v>1234.167011953736</v>
+        <v>-73.29484838522421</v>
       </c>
       <c r="D92">
-        <v>6064.347011953736</v>
+        <v>4813.067151614776</v>
       </c>
       <c r="E92">
-        <v>4710.48</v>
+        <v>4766.662</v>
       </c>
       <c r="F92">
-        <v>5056.38</v>
+        <v>5112.562</v>
       </c>
       <c r="G92">
         <v>226.2</v>
@@ -8837,45 +8837,45 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M92">
-        <v>455.0742</v>
+        <v>606.3498532000001</v>
       </c>
       <c r="N92">
-        <v>117.1339632653062</v>
+        <v>-34.14168993469389</v>
       </c>
       <c r="O92">
-        <v>35.14018897959185</v>
+        <v>-10.24250698040817</v>
       </c>
       <c r="P92">
-        <v>81.99377428571434</v>
+        <v>-23.89918295428572</v>
       </c>
       <c r="Q92">
-        <v>685.1937742857144</v>
+        <v>579.3008170457143</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7119322208302702</v>
+        <v>0.7984906663206803</v>
       </c>
       <c r="T92">
-        <v>4.64456864367114</v>
+        <v>5.248092432489805</v>
       </c>
       <c r="U92">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.3</v>
+        <v>0.2831079253563705</v>
       </c>
       <c r="W92">
-        <v>0.063</v>
+        <v>0.08502340005273447</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.257395306667146</v>
+        <v>0.9436930845212351</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1492354540168496</v>
+        <v>0.1499634540168496</v>
       </c>
       <c r="C93">
-        <v>-73.29484838522421</v>
+        <v>-163.11544955727</v>
       </c>
       <c r="D93">
-        <v>4813.067151614776</v>
+        <v>4779.42855044273</v>
       </c>
       <c r="E93">
-        <v>4766.662</v>
+        <v>4822.844</v>
       </c>
       <c r="F93">
-        <v>5112.562</v>
+        <v>5168.744</v>
       </c>
       <c r="G93">
         <v>226.2</v>
@@ -8919,37 +8919,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M93">
-        <v>606.3498532000001</v>
+        <v>613.0130384</v>
       </c>
       <c r="N93">
-        <v>-34.14168993469389</v>
+        <v>-40.80487513469382</v>
       </c>
       <c r="O93">
-        <v>-10.24250698040817</v>
+        <v>-12.24146254040815</v>
       </c>
       <c r="P93">
-        <v>-23.89918295428572</v>
+        <v>-28.56341259428567</v>
       </c>
       <c r="Q93">
-        <v>579.3008170457143</v>
+        <v>574.6365874057144</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7984906663206803</v>
+        <v>0.8925769996107655</v>
       </c>
       <c r="T93">
-        <v>5.248092432489805</v>
+        <v>5.904103986551031</v>
       </c>
       <c r="U93">
         <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.2831079253563705</v>
+        <v>0.2800306652981491</v>
       </c>
       <c r="W93">
-        <v>0.08502340005273447</v>
+        <v>0.08538836309563952</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9436930845212351</v>
+        <v>0.9334355509938306</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1499634540168496</v>
+        <v>0.1506914540168496</v>
       </c>
       <c r="C94">
-        <v>-163.11544955727</v>
+        <v>-252.4691127526676</v>
       </c>
       <c r="D94">
-        <v>4779.42855044273</v>
+        <v>4746.256887247333</v>
       </c>
       <c r="E94">
-        <v>4822.844</v>
+        <v>4879.026000000001</v>
       </c>
       <c r="F94">
-        <v>5168.744</v>
+        <v>5224.926</v>
       </c>
       <c r="G94">
         <v>226.2</v>
@@ -9001,37 +9001,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M94">
-        <v>613.0130384</v>
+        <v>619.6762236000001</v>
       </c>
       <c r="N94">
-        <v>-40.80487513469382</v>
+        <v>-47.46806033469386</v>
       </c>
       <c r="O94">
-        <v>-12.24146254040815</v>
+        <v>-14.24041810040816</v>
       </c>
       <c r="P94">
-        <v>-28.56341259428567</v>
+        <v>-33.2276422342857</v>
       </c>
       <c r="Q94">
-        <v>574.6365874057144</v>
+        <v>569.9723577657144</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8925769996107655</v>
+        <v>1.013545142412304</v>
       </c>
       <c r="T94">
-        <v>5.904103986551031</v>
+        <v>6.74754741320118</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.2800306652981491</v>
+        <v>0.2770195828755884</v>
       </c>
       <c r="W94">
-        <v>0.08538836309563952</v>
+        <v>0.08574547747095523</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9334355509938306</v>
+        <v>0.9233986095852946</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1506914540168496</v>
+        <v>0.1514194540168496</v>
       </c>
       <c r="C95">
-        <v>-252.4691127526676</v>
+        <v>-341.3654933190055</v>
       </c>
       <c r="D95">
-        <v>4746.256887247333</v>
+        <v>4713.542506680995</v>
       </c>
       <c r="E95">
-        <v>4879.026000000001</v>
+        <v>4935.208000000001</v>
       </c>
       <c r="F95">
-        <v>5224.926</v>
+        <v>5281.108</v>
       </c>
       <c r="G95">
         <v>226.2</v>
@@ -9083,37 +9083,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M95">
-        <v>619.6762236000001</v>
+        <v>626.3394088000001</v>
       </c>
       <c r="N95">
-        <v>-47.46806033469386</v>
+        <v>-54.1312455346939</v>
       </c>
       <c r="O95">
-        <v>-14.24041810040816</v>
+        <v>-16.23937366040817</v>
       </c>
       <c r="P95">
-        <v>-33.2276422342857</v>
+        <v>-37.89187187428573</v>
       </c>
       <c r="Q95">
-        <v>569.9723577657144</v>
+        <v>565.3081281257143</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.013545142412304</v>
+        <v>1.174835999481021</v>
       </c>
       <c r="T95">
-        <v>6.74754741320118</v>
+        <v>7.872138648734712</v>
       </c>
       <c r="U95">
         <v>0.1186</v>
       </c>
       <c r="V95">
-        <v>0.2770195828755884</v>
+        <v>0.2740725660364863</v>
       </c>
       <c r="W95">
-        <v>0.08574547747095523</v>
+        <v>0.08609499366807273</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9233986095852946</v>
+        <v>0.9135752201216212</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1514194540168496</v>
+        <v>0.1521474540168496</v>
       </c>
       <c r="C96">
-        <v>-341.3654933190055</v>
+        <v>-429.8139822216935</v>
       </c>
       <c r="D96">
-        <v>4713.542506680995</v>
+        <v>4681.276017778307</v>
       </c>
       <c r="E96">
-        <v>4935.208000000001</v>
+        <v>4991.39</v>
       </c>
       <c r="F96">
-        <v>5281.108</v>
+        <v>5337.29</v>
       </c>
       <c r="G96">
         <v>226.2</v>
@@ -9165,37 +9165,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M96">
-        <v>626.3394088000001</v>
+        <v>633.002594</v>
       </c>
       <c r="N96">
-        <v>-54.1312455346939</v>
+        <v>-60.79443073469383</v>
       </c>
       <c r="O96">
-        <v>-16.23937366040817</v>
+        <v>-18.23832922040815</v>
       </c>
       <c r="P96">
-        <v>-37.89187187428573</v>
+        <v>-42.55610151428569</v>
       </c>
       <c r="Q96">
-        <v>565.3081281257143</v>
+        <v>560.6438984857143</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.174835999481021</v>
+        <v>1.400643199377226</v>
       </c>
       <c r="T96">
-        <v>7.872138648734712</v>
+        <v>9.446566378481659</v>
       </c>
       <c r="U96">
         <v>0.1186</v>
       </c>
       <c r="V96">
-        <v>0.2740725660364863</v>
+        <v>0.2711875916571549</v>
       </c>
       <c r="W96">
-        <v>0.08609499366807273</v>
+        <v>0.08643715162946143</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9135752201216212</v>
+        <v>0.9039586388571832</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1521474540168496</v>
+        <v>0.1528754540168496</v>
       </c>
       <c r="C97">
-        <v>-429.8139822216935</v>
+        <v>-517.8237150315526</v>
       </c>
       <c r="D97">
-        <v>4681.276017778307</v>
+        <v>4649.448284968448</v>
       </c>
       <c r="E97">
-        <v>4991.39</v>
+        <v>5047.572000000001</v>
       </c>
       <c r="F97">
-        <v>5337.29</v>
+        <v>5393.472000000001</v>
       </c>
       <c r="G97">
         <v>226.2</v>
@@ -9247,37 +9247,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M97">
-        <v>633.002594</v>
+        <v>639.6657792000001</v>
       </c>
       <c r="N97">
-        <v>-60.79443073469383</v>
+        <v>-67.45761593469388</v>
       </c>
       <c r="O97">
-        <v>-18.23832922040815</v>
+        <v>-20.23728478040816</v>
       </c>
       <c r="P97">
-        <v>-42.55610151428569</v>
+        <v>-47.22033115428572</v>
       </c>
       <c r="Q97">
-        <v>560.6438984857143</v>
+        <v>555.9796688457143</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.400643199377226</v>
+        <v>1.739353999221533</v>
       </c>
       <c r="T97">
-        <v>9.446566378481659</v>
+        <v>11.80820797310208</v>
       </c>
       <c r="U97">
         <v>0.1186</v>
       </c>
       <c r="V97">
-        <v>0.2711875916571549</v>
+        <v>0.2683627209107262</v>
       </c>
       <c r="W97">
-        <v>0.08643715162946143</v>
+        <v>0.08677218129998789</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9039586388571832</v>
+        <v>0.8945424030357542</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1528754540168496</v>
+        <v>0.1536034540168495</v>
       </c>
       <c r="C98">
-        <v>-517.8237150315499</v>
+        <v>-605.4035805482517</v>
       </c>
       <c r="D98">
-        <v>4649.44828496845</v>
+        <v>4618.050419451748</v>
       </c>
       <c r="E98">
-        <v>5047.572</v>
+        <v>5103.754</v>
       </c>
       <c r="F98">
-        <v>5393.472</v>
+        <v>5449.654</v>
       </c>
       <c r="G98">
         <v>226.2</v>
@@ -9329,37 +9329,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M98">
-        <v>639.6657792</v>
+        <v>646.3289644</v>
       </c>
       <c r="N98">
-        <v>-67.45761593469376</v>
+        <v>-74.12080113469381</v>
       </c>
       <c r="O98">
-        <v>-20.23728478040813</v>
+        <v>-22.23624034040814</v>
       </c>
       <c r="P98">
-        <v>-47.22033115428563</v>
+        <v>-51.88456079428566</v>
       </c>
       <c r="Q98">
-        <v>555.9796688457144</v>
+        <v>551.3154392057144</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.739353999221529</v>
+        <v>2.303871998962038</v>
       </c>
       <c r="T98">
-        <v>11.80820797310205</v>
+        <v>15.7442772974694</v>
       </c>
       <c r="U98">
         <v>0.1186</v>
       </c>
       <c r="V98">
-        <v>0.2683627209107263</v>
+        <v>0.2655960949219559</v>
       </c>
       <c r="W98">
-        <v>0.08677218129998789</v>
+        <v>0.08710030314225604</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8945424030357543</v>
+        <v>0.8853203164065196</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1536034540168495</v>
+        <v>0.1543314540168496</v>
       </c>
       <c r="C99">
-        <v>-605.4035805482517</v>
+        <v>-692.5622290766951</v>
       </c>
       <c r="D99">
-        <v>4618.050419451748</v>
+        <v>4587.073770923304</v>
       </c>
       <c r="E99">
-        <v>5103.754</v>
+        <v>5159.936</v>
       </c>
       <c r="F99">
-        <v>5449.654</v>
+        <v>5505.835999999999</v>
       </c>
       <c r="G99">
         <v>226.2</v>
@@ -9411,37 +9411,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M99">
-        <v>646.3289644</v>
+        <v>652.9921495999999</v>
       </c>
       <c r="N99">
-        <v>-74.12080113469381</v>
+        <v>-80.78398633469374</v>
       </c>
       <c r="O99">
-        <v>-22.23624034040814</v>
+        <v>-24.23519590040812</v>
       </c>
       <c r="P99">
-        <v>-51.88456079428566</v>
+        <v>-56.54879043428562</v>
       </c>
       <c r="Q99">
-        <v>551.3154392057144</v>
+        <v>546.6512095657145</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.303871998962038</v>
+        <v>3.432907998443057</v>
       </c>
       <c r="T99">
-        <v>15.7442772974694</v>
+        <v>23.61641594620409</v>
       </c>
       <c r="U99">
         <v>0.1186</v>
       </c>
       <c r="V99">
-        <v>0.2655960949219559</v>
+        <v>0.2628859306880584</v>
       </c>
       <c r="W99">
-        <v>0.08710030314225604</v>
+        <v>0.08742172862039628</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8853203164065196</v>
+        <v>0.8762864356268614</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1543314540168496</v>
+        <v>0.1550594540168496</v>
       </c>
       <c r="C100">
-        <v>-692.5622290766951</v>
+        <v>-779.3080803725043</v>
       </c>
       <c r="D100">
-        <v>4587.073770923304</v>
+        <v>4556.509919627496</v>
       </c>
       <c r="E100">
-        <v>5159.936</v>
+        <v>5216.118</v>
       </c>
       <c r="F100">
-        <v>5505.835999999999</v>
+        <v>5562.018</v>
       </c>
       <c r="G100">
         <v>226.2</v>
@@ -9493,37 +9493,37 @@
         <v>572.2081632653062</v>
       </c>
       <c r="M100">
-        <v>652.9921495999999</v>
+        <v>659.6553348000001</v>
       </c>
       <c r="N100">
-        <v>-80.78398633469374</v>
+        <v>-87.44717153469389</v>
       </c>
       <c r="O100">
-        <v>-24.23519590040812</v>
+        <v>-26.23415146040817</v>
       </c>
       <c r="P100">
-        <v>-56.54879043428562</v>
+        <v>-61.21302007428572</v>
       </c>
       <c r="Q100">
-        <v>546.6512095657145</v>
+        <v>541.9869799257143</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.432907998443057</v>
+        <v>6.820015996886115</v>
       </c>
       <c r="T100">
-        <v>23.61641594620409</v>
+        <v>47.23283189240819</v>
       </c>
       <c r="U100">
         <v>0.1186</v>
       </c>
       <c r="V100">
-        <v>0.2628859306880584</v>
+        <v>0.2602305172467648</v>
       </c>
       <c r="W100">
-        <v>0.08742172862039628</v>
+        <v>0.0877366606545337</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8762864356268614</v>
+        <v>0.8674350574892161</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1550594540168496</v>
-      </c>
-      <c r="C101">
-        <v>-779.3080803725043</v>
-      </c>
-      <c r="D101">
-        <v>4556.509919627496</v>
-      </c>
-      <c r="E101">
-        <v>5216.118</v>
-      </c>
-      <c r="F101">
-        <v>5562.018</v>
-      </c>
-      <c r="G101">
-        <v>226.2</v>
-      </c>
-      <c r="H101">
-        <v>5272.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1175.408163265306</v>
-      </c>
-      <c r="K101">
-        <v>603.2</v>
-      </c>
-      <c r="L101">
-        <v>572.2081632653062</v>
-      </c>
-      <c r="M101">
-        <v>659.6553348000001</v>
-      </c>
-      <c r="N101">
-        <v>-87.44717153469389</v>
-      </c>
-      <c r="O101">
-        <v>-26.23415146040817</v>
-      </c>
-      <c r="P101">
-        <v>-61.21302007428572</v>
-      </c>
-      <c r="Q101">
-        <v>541.9869799257143</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.820015996886115</v>
-      </c>
-      <c r="T101">
-        <v>47.23283189240819</v>
-      </c>
-      <c r="U101">
-        <v>0.1186</v>
-      </c>
-      <c r="V101">
-        <v>0.2602305172467648</v>
-      </c>
-      <c r="W101">
-        <v>0.0877366606545337</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8674350574892161</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
